--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>06/09/2026 09:57:33</t>
+          <t>07/09/2026 12:13:15</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>07/09/2026 12:13:15</t>
+          <t>08/09/2026 10:36:35</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>118595.35</v>
+        <v>125073.21</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5033812.52</v>
+        <v>5081204.36</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>20257146.43</v>
       </c>
       <c r="S10" t="n">
-        <v>9705526.23</v>
+        <v>9718071.23</v>
       </c>
       <c r="T10" t="n">
-        <v>11248777.65</v>
+        <v>11261322.65</v>
       </c>
       <c r="U10" t="n">
         <v>11868232.01</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>81465.10000000001</v>
+        <v>84484.75999999999</v>
       </c>
       <c r="S17" t="n">
         <v>69900.72</v>
@@ -2778,7 +2778,7 @@
         <v>69900.72</v>
       </c>
       <c r="U17" t="n">
-        <v>71456.17999999999</v>
+        <v>74475.84</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1147094.82</v>
+        <v>1147974.94</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4589,16 +4589,16 @@
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2600214.6</v>
+        <v>2634091.06</v>
       </c>
       <c r="S30" t="n">
-        <v>1796983.06</v>
+        <v>1812267.57</v>
       </c>
       <c r="T30" t="n">
-        <v>1953573.84</v>
+        <v>1968858.35</v>
       </c>
       <c r="U30" t="n">
-        <v>1946992.85</v>
+        <v>1980869.31</v>
       </c>
       <c r="V30" t="n">
         <v>156590.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2692507.2</v>
+        <v>2702416.24</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -4872,10 +4872,10 @@
         <v>24790341.23</v>
       </c>
       <c r="S32" t="n">
-        <v>17430458.27</v>
+        <v>17465577.71</v>
       </c>
       <c r="T32" t="n">
-        <v>21213481.21</v>
+        <v>21248600.65</v>
       </c>
       <c r="U32" t="n">
         <v>18678619.8</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1907666.15</v>
+        <v>1908014.44</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>657979.71</v>
       </c>
       <c r="M88" t="n">
         <v>0</v>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -13832,10 +13832,10 @@
         <v>100000</v>
       </c>
       <c r="S96" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="T96" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U96" t="n">
         <v>100000</v>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -14791,7 +14791,7 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>276820.97</v>
+        <v>286730.01</v>
       </c>
       <c r="M103" t="n">
         <v>0</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>7195593.68</v>
+        <v>7207451.3</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -25991,7 +25991,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="M183" t="n">
         <v>0</v>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26280,7 +26280,7 @@
         <v>371000</v>
       </c>
       <c r="O185" t="n">
-        <v>6275600</v>
+        <v>7108000</v>
       </c>
       <c r="P185" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>774265.55</v>
+        <v>784174.59</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28949,7 @@
         <v>39738</v>
       </c>
       <c r="R204" t="n">
-        <v>46600</v>
+        <v>48000</v>
       </c>
       <c r="S204" t="n">
         <v>32500</v>
@@ -28958,7 +28958,7 @@
         <v>33100</v>
       </c>
       <c r="U204" t="n">
-        <v>35200</v>
+        <v>36600</v>
       </c>
       <c r="V204" t="n">
         <v>600</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>08/09/2026 10:36:35</t>
+          <t>09/09/2026 10:49:41</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>163512.81</v>
       </c>
       <c r="P7" t="n">
-        <v>377087.59</v>
+        <v>449293.59</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>1038931.04</v>
+        <v>1110619.55</v>
       </c>
       <c r="S7" t="n">
         <v>460484.87</v>
@@ -1378,7 +1378,7 @@
         <v>565484.87</v>
       </c>
       <c r="U7" t="n">
-        <v>661843.45</v>
+        <v>661325.96</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5081204.36</v>
+        <v>5238981.69</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,25 +1780,25 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4742385.19</v>
+        <v>4761581.79</v>
       </c>
       <c r="P10" t="n">
-        <v>8388914.42</v>
+        <v>9007845.380000001</v>
       </c>
       <c r="Q10" t="n">
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>20257146.43</v>
+        <v>20960210.72</v>
       </c>
       <c r="S10" t="n">
-        <v>9718071.23</v>
+        <v>10596990.55</v>
       </c>
       <c r="T10" t="n">
-        <v>11261322.65</v>
+        <v>12140241.97</v>
       </c>
       <c r="U10" t="n">
-        <v>11868232.01</v>
+        <v>11952365.34</v>
       </c>
       <c r="V10" t="n">
         <v>1543251.42</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>84484.75999999999</v>
+        <v>88366.42</v>
       </c>
       <c r="S17" t="n">
         <v>69900.72</v>
@@ -2778,7 +2778,7 @@
         <v>69900.72</v>
       </c>
       <c r="U17" t="n">
-        <v>74475.84</v>
+        <v>78357.5</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
         <v>50000</v>
       </c>
       <c r="R24" t="n">
-        <v>85353.67999999999</v>
+        <v>131343.68</v>
       </c>
       <c r="S24" t="n">
         <v>6040.6</v>
@@ -3758,7 +3758,7 @@
         <v>6040.6</v>
       </c>
       <c r="U24" t="n">
-        <v>16889.62</v>
+        <v>62879.62</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1147974.94</v>
+        <v>1280448.06</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4589,19 +4589,19 @@
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2634091.06</v>
+        <v>2635291.06</v>
       </c>
       <c r="S30" t="n">
-        <v>1812267.57</v>
+        <v>1813467.57</v>
       </c>
       <c r="T30" t="n">
-        <v>1968858.35</v>
+        <v>1970658.35</v>
       </c>
       <c r="U30" t="n">
-        <v>1980869.31</v>
+        <v>1982069.31</v>
       </c>
       <c r="V30" t="n">
-        <v>156590.78</v>
+        <v>157190.78</v>
       </c>
       <c r="W30" t="n">
         <v>2102736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>9491342.73</v>
+        <v>10282176.34</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1908014.44</v>
+        <v>1911654.51</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6400,16 +6400,16 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>9985.280000000001</v>
+        <v>10313.28</v>
       </c>
       <c r="P43" t="n">
-        <v>98795.48</v>
+        <v>114195.48</v>
       </c>
       <c r="Q43" t="n">
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>327572.54</v>
+        <v>342938.94</v>
       </c>
       <c r="S43" t="n">
         <v>68323.37</v>
@@ -6418,7 +6418,7 @@
         <v>72259.37</v>
       </c>
       <c r="U43" t="n">
-        <v>228777.06</v>
+        <v>228743.46</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2730193.85</v>
+        <v>2831932.72</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>2716076.57</v>
+        <v>2718069.51</v>
       </c>
       <c r="P46" t="n">
         <v>17377529.65</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7672,10 +7672,10 @@
         <v>13881760.97</v>
       </c>
       <c r="S52" t="n">
-        <v>9042518.710000001</v>
+        <v>9291804.449999999</v>
       </c>
       <c r="T52" t="n">
-        <v>11696727.44</v>
+        <v>11946013.18</v>
       </c>
       <c r="U52" t="n">
         <v>9291804.449999999</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -12831,7 +12831,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>993550</v>
+        <v>1128400</v>
       </c>
       <c r="M89" t="n">
         <v>0</v>
@@ -12852,16 +12852,16 @@
         <v>1800000</v>
       </c>
       <c r="S89" t="n">
-        <v>1010600</v>
+        <v>1128400</v>
       </c>
       <c r="T89" t="n">
-        <v>1010600</v>
+        <v>1145450</v>
       </c>
       <c r="U89" t="n">
         <v>1800000</v>
       </c>
       <c r="V89" t="n">
-        <v>0</v>
+        <v>17050</v>
       </c>
       <c r="W89" t="n">
         <v>1800000</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14669,7 @@
         <v>30045</v>
       </c>
       <c r="R102" t="n">
-        <v>93241.23</v>
+        <v>106235.82</v>
       </c>
       <c r="S102" t="n">
         <v>76123.00999999999</v>
@@ -14678,7 +14678,7 @@
         <v>76123.00999999999</v>
       </c>
       <c r="U102" t="n">
-        <v>92005.41</v>
+        <v>105000</v>
       </c>
       <c r="V102" t="n">
         <v>0</v>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16063,13 +16063,13 @@
         <v>184781.14</v>
       </c>
       <c r="P112" t="n">
-        <v>39372.12</v>
+        <v>50000</v>
       </c>
       <c r="Q112" t="n">
         <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>432124.12</v>
+        <v>442635.02</v>
       </c>
       <c r="S112" t="n">
         <v>363452.83</v>
@@ -16078,7 +16078,7 @@
         <v>363452.83</v>
       </c>
       <c r="U112" t="n">
-        <v>392752</v>
+        <v>392635.02</v>
       </c>
       <c r="V112" t="n">
         <v>0</v>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21651,7 +21651,7 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>1456637.56</v>
+        <v>1458637.56</v>
       </c>
       <c r="M152" t="n">
         <v>0</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23060,7 +23060,7 @@
         <v>259262</v>
       </c>
       <c r="O162" t="n">
-        <v>46763.29</v>
+        <v>74047.78999999999</v>
       </c>
       <c r="P162" t="n">
         <v>679875.02</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>211572</v>
       </c>
       <c r="O164" t="n">
-        <v>1769046.36</v>
+        <v>1771091.44</v>
       </c>
       <c r="P164" t="n">
         <v>2709234.52</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26292,7 +26292,7 @@
         <v>9076439.67</v>
       </c>
       <c r="S185" t="n">
-        <v>7188000</v>
+        <v>7108000</v>
       </c>
       <c r="T185" t="n">
         <v>8061200</v>
@@ -26301,7 +26301,7 @@
         <v>9076439.67</v>
       </c>
       <c r="V185" t="n">
-        <v>873200</v>
+        <v>953200</v>
       </c>
       <c r="W185" t="n">
         <v>9076439.67</v>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -28952,10 +28952,10 @@
         <v>48000</v>
       </c>
       <c r="S204" t="n">
-        <v>32500</v>
+        <v>36000</v>
       </c>
       <c r="T204" t="n">
-        <v>33100</v>
+        <v>36600</v>
       </c>
       <c r="U204" t="n">
         <v>36600</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30489,7 +30489,7 @@
         <v>5086650.13</v>
       </c>
       <c r="R215" t="n">
-        <v>215048522.8</v>
+        <v>215486986.5</v>
       </c>
       <c r="S215" t="n">
         <v>163819531.01</v>
@@ -30498,7 +30498,7 @@
         <v>169486907.25</v>
       </c>
       <c r="U215" t="n">
-        <v>165240001.76</v>
+        <v>165678465.46</v>
       </c>
       <c r="V215" t="n">
         <v>5667376.24</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>09/09/2026 10:49:41</t>
+          <t>10/09/2026 10:39:11</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>4561253.34</v>
+        <v>5068732.62</v>
       </c>
       <c r="P3" t="n">
         <v>220570.58</v>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>103799.18</v>
+        <v>227406.29</v>
       </c>
       <c r="S6" t="n">
         <v>79745.89</v>
@@ -1238,7 +1238,7 @@
         <v>96171.98</v>
       </c>
       <c r="U6" t="n">
-        <v>79745.89</v>
+        <v>203353</v>
       </c>
       <c r="V6" t="n">
         <v>16426.09</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
         <v>163512.81</v>
       </c>
       <c r="P7" t="n">
-        <v>449293.59</v>
+        <v>462405.59</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
@@ -1378,7 +1378,7 @@
         <v>565484.87</v>
       </c>
       <c r="U7" t="n">
-        <v>661325.96</v>
+        <v>648213.96</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4761581.79</v>
+        <v>4771269.78</v>
       </c>
       <c r="P10" t="n">
         <v>9007845.380000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>349</v>
       </c>
       <c r="R29" t="n">
-        <v>40000</v>
+        <v>90000</v>
       </c>
       <c r="S29" t="n">
         <v>20000</v>
@@ -4458,7 +4458,7 @@
         <v>20000</v>
       </c>
       <c r="U29" t="n">
-        <v>20000</v>
+        <v>70000</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1280448.06</v>
+        <v>1285355.23</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,25 +4580,25 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1145867.82</v>
+        <v>1147094.82</v>
       </c>
       <c r="P30" t="n">
-        <v>653221.75</v>
+        <v>657930.84</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2635291.06</v>
+        <v>2760652.17</v>
       </c>
       <c r="S30" t="n">
-        <v>1813467.57</v>
+        <v>1832828.73</v>
       </c>
       <c r="T30" t="n">
-        <v>1970658.35</v>
+        <v>1990019.51</v>
       </c>
       <c r="U30" t="n">
-        <v>1982069.31</v>
+        <v>2102721.33</v>
       </c>
       <c r="V30" t="n">
         <v>157190.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10282176.34</v>
+        <v>10581490.38</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,16 +4860,16 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9490556.18</v>
+        <v>9490843.02</v>
       </c>
       <c r="P32" t="n">
-        <v>6111721.43</v>
+        <v>6152628.09</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>24790341.23</v>
+        <v>24832116.09</v>
       </c>
       <c r="S32" t="n">
         <v>17465577.71</v>
@@ -4878,7 +4878,7 @@
         <v>21248600.65</v>
       </c>
       <c r="U32" t="n">
-        <v>18678619.8</v>
+        <v>18679488</v>
       </c>
       <c r="V32" t="n">
         <v>3783022.94</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5000,10 +5000,10 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>432521.77</v>
+        <v>436865.44</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -5018,7 +5018,7 @@
         <v>919904.16</v>
       </c>
       <c r="U33" t="n">
-        <v>970517</v>
+        <v>958517</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6680,7 +6680,7 @@
         <v>1006324.68</v>
       </c>
       <c r="O45" t="n">
-        <v>706433.0600000001</v>
+        <v>825646.38</v>
       </c>
       <c r="P45" t="n">
         <v>1473433.88</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7669,7 +7669,7 @@
         <v>278000</v>
       </c>
       <c r="R52" t="n">
-        <v>13881760.97</v>
+        <v>13892639.52</v>
       </c>
       <c r="S52" t="n">
         <v>9291804.449999999</v>
@@ -7678,7 +7678,7 @@
         <v>11946013.18</v>
       </c>
       <c r="U52" t="n">
-        <v>9291804.449999999</v>
+        <v>9302683</v>
       </c>
       <c r="V52" t="n">
         <v>2654208.73</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8649,7 +8649,7 @@
         <v>1514015.72</v>
       </c>
       <c r="R59" t="n">
-        <v>25582815.93</v>
+        <v>25835164.83</v>
       </c>
       <c r="S59" t="n">
         <v>18060730.63</v>
@@ -8658,7 +8658,7 @@
         <v>23740438.8</v>
       </c>
       <c r="U59" t="n">
-        <v>18266410.1</v>
+        <v>18518759</v>
       </c>
       <c r="V59" t="n">
         <v>5679708.17</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18452,10 +18452,10 @@
         <v>130000</v>
       </c>
       <c r="S129" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="T129" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="U129" t="n">
         <v>130000</v>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20260,7 +20260,7 @@
         <v>0</v>
       </c>
       <c r="O142" t="n">
-        <v>7195593.68</v>
+        <v>7207451.3</v>
       </c>
       <c r="P142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21660,7 @@
         <v>0</v>
       </c>
       <c r="O152" t="n">
-        <v>1405137.56</v>
+        <v>1450137.56</v>
       </c>
       <c r="P152" t="n">
         <v>16244437.91</v>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22083,7 +22083,7 @@
         <v>9099.6</v>
       </c>
       <c r="P155" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="Q155" t="n">
         <v>0</v>
@@ -22098,7 +22098,7 @@
         <v>18388</v>
       </c>
       <c r="U155" t="n">
-        <v>107627.35</v>
+        <v>40627.35</v>
       </c>
       <c r="V155" t="n">
         <v>0</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23480,7 +23480,7 @@
         <v>158000</v>
       </c>
       <c r="O165" t="n">
-        <v>134010.89</v>
+        <v>147652.91</v>
       </c>
       <c r="P165" t="n">
         <v>0</v>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24460,7 +24460,7 @@
         <v>60000</v>
       </c>
       <c r="O172" t="n">
-        <v>0</v>
+        <v>60000</v>
       </c>
       <c r="P172" t="n">
         <v>0</v>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25440,7 +25440,7 @@
         <v>578000</v>
       </c>
       <c r="O179" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="P179" t="n">
         <v>0</v>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
         <v>82853.60000000001</v>
       </c>
       <c r="P187" t="n">
-        <v>46171.82</v>
+        <v>66171.82000000001</v>
       </c>
       <c r="Q187" t="n">
         <v>0</v>
@@ -26578,7 +26578,7 @@
         <v>164926.33</v>
       </c>
       <c r="U187" t="n">
-        <v>221737.33</v>
+        <v>201737.33</v>
       </c>
       <c r="V187" t="n">
         <v>3532.21</v>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -26840,7 +26840,7 @@
         <v>0</v>
       </c>
       <c r="O189" t="n">
-        <v>744555.9399999999</v>
+        <v>774265.55</v>
       </c>
       <c r="P189" t="n">
         <v>1760683.97</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28529,7 +28529,7 @@
         <v>5054381</v>
       </c>
       <c r="R201" t="n">
-        <v>7689959.02</v>
+        <v>7758858.94</v>
       </c>
       <c r="S201" t="n">
         <v>559609.14</v>
@@ -28538,7 +28538,7 @@
         <v>2453838.77</v>
       </c>
       <c r="U201" t="n">
-        <v>4732638.08</v>
+        <v>4801538</v>
       </c>
       <c r="V201" t="n">
         <v>1894229.63</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
         <v>5686650.13</v>
       </c>
       <c r="O211" t="n">
-        <v>30296477.82</v>
+        <v>34068633.7</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30471,7 +30471,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>141029238.38</v>
+        <v>141048635.1</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -30480,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>135617990.41</v>
+        <v>138273116.26</v>
       </c>
       <c r="P215" t="n">
         <v>49808521.04</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
         <v>0</v>
       </c>
       <c r="O218" t="n">
-        <v>69557963.70999999</v>
+        <v>71986213.70999999</v>
       </c>
       <c r="P218" t="n">
         <v>62818272</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>54741982.83</v>
+        <v>54893496.57</v>
       </c>
       <c r="P219" t="n">
         <v>50438263.91</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>
@@ -32020,16 +32020,16 @@
         <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>35362303.78</v>
+        <v>36382287.88</v>
       </c>
       <c r="P226" t="n">
-        <v>6952882.48</v>
+        <v>7296374.48</v>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>49535258.91</v>
+        <v>49878750.91</v>
       </c>
       <c r="S226" t="n">
         <v>39557476.52</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>10/09/2026 10:39:11</t>
+          <t>11/09/2026 10:41:55</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5238981.69</v>
+        <v>5472882.11</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>295928.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4771269.78</v>
+        <v>4789607.38</v>
       </c>
       <c r="P10" t="n">
         <v>9007845.380000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>182618.64</v>
+        <v>189987.88</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1028688.4</v>
+        <v>1185724.86</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3509598.53</v>
+        <v>3515358.53</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1285355.23</v>
+        <v>1303727.73</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10581490.38</v>
+        <v>10795877.49</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9490843.02</v>
+        <v>9491342.720000001</v>
       </c>
       <c r="P32" t="n">
         <v>6152628.09</v>
@@ -4872,10 +4872,10 @@
         <v>24832116.09</v>
       </c>
       <c r="S32" t="n">
-        <v>17465577.71</v>
+        <v>18305143.71</v>
       </c>
       <c r="T32" t="n">
-        <v>21248600.65</v>
+        <v>22088166.65</v>
       </c>
       <c r="U32" t="n">
         <v>18679488</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>438489.3</v>
+        <v>469627.74</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>82538.81</v>
+        <v>98254.77</v>
       </c>
       <c r="P34" t="n">
         <v>226413.89</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1908014.44</v>
+        <v>1908345.94</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6412,10 +6412,10 @@
         <v>342938.94</v>
       </c>
       <c r="S43" t="n">
-        <v>68323.37</v>
+        <v>114323.37</v>
       </c>
       <c r="T43" t="n">
-        <v>72259.37</v>
+        <v>118259.37</v>
       </c>
       <c r="U43" t="n">
         <v>228743.46</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2831932.72</v>
+        <v>3066699.43</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11571,7 +11571,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>439634</v>
       </c>
       <c r="M80" t="n">
         <v>0</v>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12152,10 +12152,10 @@
         <v>250000</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="U84" t="n">
         <v>250000</v>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>99996</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -13138,7 +13138,7 @@
         <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>0</v>
+        <v>99996</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14091,7 +14091,7 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>22092.87</v>
       </c>
       <c r="M98" t="n">
         <v>0</v>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14800,7 +14800,7 @@
         <v>0</v>
       </c>
       <c r="O103" t="n">
-        <v>245768.58</v>
+        <v>276820.97</v>
       </c>
       <c r="P103" t="n">
         <v>150685.93</v>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -14931,7 +14931,7 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>114042.91</v>
+        <v>114466.75</v>
       </c>
       <c r="M104" t="n">
         <v>0</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17192,10 +17192,10 @@
         <v>172841.29</v>
       </c>
       <c r="S120" t="n">
-        <v>80142</v>
+        <v>85742</v>
       </c>
       <c r="T120" t="n">
-        <v>80142</v>
+        <v>85742</v>
       </c>
       <c r="U120" t="n">
         <v>172519.48</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17469,7 +17469,7 @@
         <v>50000</v>
       </c>
       <c r="R122" t="n">
-        <v>28579.31</v>
+        <v>36599.31</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -17478,7 +17478,7 @@
         <v>0</v>
       </c>
       <c r="U122" t="n">
-        <v>26579.31</v>
+        <v>34599.31</v>
       </c>
       <c r="V122" t="n">
         <v>0</v>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18732,10 +18732,10 @@
         <v>400000</v>
       </c>
       <c r="S131" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="T131" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="U131" t="n">
         <v>400000</v>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19569,7 +19569,7 @@
         <v>0</v>
       </c>
       <c r="R137" t="n">
-        <v>17227496.93</v>
+        <v>18983976.92</v>
       </c>
       <c r="S137" t="n">
         <v>8445809.92</v>
@@ -19578,7 +19578,7 @@
         <v>8445809.92</v>
       </c>
       <c r="U137" t="n">
-        <v>10919153.01</v>
+        <v>12675633</v>
       </c>
       <c r="V137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20272,10 +20272,10 @@
         <v>9748668.68</v>
       </c>
       <c r="S142" t="n">
-        <v>7383237.78</v>
+        <v>9748668.68</v>
       </c>
       <c r="T142" t="n">
-        <v>7383237.78</v>
+        <v>9748668.68</v>
       </c>
       <c r="U142" t="n">
         <v>9748668.68</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22351,7 +22351,7 @@
         </is>
       </c>
       <c r="L157" t="n">
-        <v>236546.44</v>
+        <v>237363.41</v>
       </c>
       <c r="M157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23051,7 +23051,7 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>134059.79</v>
+        <v>136238.21</v>
       </c>
       <c r="M162" t="n">
         <v>0</v>
@@ -23060,7 +23060,7 @@
         <v>259262</v>
       </c>
       <c r="O162" t="n">
-        <v>74047.78999999999</v>
+        <v>133731.79</v>
       </c>
       <c r="P162" t="n">
         <v>679875.02</v>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23200,7 +23200,7 @@
         <v>564000</v>
       </c>
       <c r="O163" t="n">
-        <v>485922.72</v>
+        <v>566909.84</v>
       </c>
       <c r="P163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23331,7 +23331,7 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>1772047.84</v>
+        <v>1773004.24</v>
       </c>
       <c r="M164" t="n">
         <v>0</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25032,10 +25032,10 @@
         <v>100000</v>
       </c>
       <c r="S176" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="T176" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="U176" t="n">
         <v>100000</v>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25732,10 +25732,10 @@
         <v>261000</v>
       </c>
       <c r="S181" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="U181" t="n">
         <v>261000</v>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26420,7 @@
         <v>2800000</v>
       </c>
       <c r="O186" t="n">
-        <v>24420778.67</v>
+        <v>24545612.47</v>
       </c>
       <c r="P186" t="n">
         <v>1885306.26</v>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26691,7 +26691,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>84789.60000000001</v>
+        <v>95912.85000000001</v>
       </c>
       <c r="M188" t="n">
         <v>0</v>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -26971,7 +26971,7 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>1573472.63</v>
+        <v>1625643.01</v>
       </c>
       <c r="M190" t="n">
         <v>0</v>
@@ -26992,10 +26992,10 @@
         <v>5642757.56</v>
       </c>
       <c r="S190" t="n">
-        <v>2403429.22</v>
+        <v>2470271.07</v>
       </c>
       <c r="T190" t="n">
-        <v>2507776.98</v>
+        <v>2574618.83</v>
       </c>
       <c r="U190" t="n">
         <v>3325758.91</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27251,7 +27251,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>13774.95</v>
+        <v>15742.8</v>
       </c>
       <c r="M192" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -29920,7 +29920,7 @@
         <v>5686650.13</v>
       </c>
       <c r="O211" t="n">
-        <v>34068633.7</v>
+        <v>34668633.7</v>
       </c>
       <c r="P211" t="n">
         <v>0</v>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30471,7 +30471,7 @@
         </is>
       </c>
       <c r="L215" t="n">
-        <v>141048635.1</v>
+        <v>143098928.32</v>
       </c>
       <c r="M215" t="n">
         <v>0</v>
@@ -30480,7 +30480,7 @@
         <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>138273116.26</v>
+        <v>139588507.36</v>
       </c>
       <c r="P215" t="n">
         <v>49808521.04</v>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>55047627.33</v>
+        <v>55125882.9</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>
@@ -32029,7 +32029,7 @@
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>49878750.91</v>
+        <v>50222242.91</v>
       </c>
       <c r="S226" t="n">
         <v>39557476.52</v>
@@ -32038,7 +32038,7 @@
         <v>41170240.68</v>
       </c>
       <c r="U226" t="n">
-        <v>42582376.43</v>
+        <v>42925868.43</v>
       </c>
       <c r="V226" t="n">
         <v>1612764.16</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>11/09/2026 10:41:55</t>
+          <t>13/09/2026 10:59:10</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>13/09/2026 10:59:10</t>
+          <t>14/09/2026 12:59:26</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1223,13 +1223,13 @@
         <v>79745.89</v>
       </c>
       <c r="P6" t="n">
-        <v>24053.29</v>
+        <v>24908.29</v>
       </c>
       <c r="Q6" t="n">
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>227406.29</v>
+        <v>228261.29</v>
       </c>
       <c r="S6" t="n">
         <v>79745.89</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5472882.11</v>
+        <v>5476437.15</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1792,10 +1792,10 @@
         <v>20960210.72</v>
       </c>
       <c r="S10" t="n">
-        <v>10596990.55</v>
+        <v>10600054.84</v>
       </c>
       <c r="T10" t="n">
-        <v>12140241.97</v>
+        <v>12143306.26</v>
       </c>
       <c r="U10" t="n">
         <v>11952365.34</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3515358.53</v>
+        <v>3516525.19</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10795877.49</v>
+        <v>10796801.49</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4872,10 +4872,10 @@
         <v>24832116.09</v>
       </c>
       <c r="S32" t="n">
-        <v>18305143.71</v>
+        <v>18457507.97</v>
       </c>
       <c r="T32" t="n">
-        <v>22088166.65</v>
+        <v>22240530.91</v>
       </c>
       <c r="U32" t="n">
         <v>18679488</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1908345.94</v>
+        <v>1911654.51</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -6844,7 +6844,7 @@
         <v>500449.56</v>
       </c>
       <c r="W46" t="n">
-        <v>14320561.05</v>
+        <v>14282561.05</v>
       </c>
       <c r="X46" t="n">
         <v>21072104</v>
@@ -6853,10 +6853,10 @@
         <v>5379029</v>
       </c>
       <c r="Z46" t="n">
-        <v>6845428.95</v>
+        <v>6883428.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>14320561.05</v>
+        <v>14282561.05</v>
       </c>
       <c r="AB46" t="n">
         <v>5</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7237,7 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>8100</v>
+        <v>46100</v>
       </c>
       <c r="O49" t="n">
         <v>7939.96</v>
@@ -7264,7 +7264,7 @@
         <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>8100</v>
+        <v>46100</v>
       </c>
       <c r="X49" t="n">
         <v>0</v>
@@ -7276,7 +7276,7 @@
         <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>8100</v>
+        <v>46100</v>
       </c>
       <c r="AB49" t="n">
         <v>5</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8372,10 +8372,10 @@
         <v>330000</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>330000</v>
       </c>
       <c r="U57" t="n">
         <v>330000</v>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12292,10 +12292,10 @@
         <v>107000</v>
       </c>
       <c r="S85" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="T85" t="n">
-        <v>0</v>
+        <v>107000</v>
       </c>
       <c r="U85" t="n">
         <v>107000</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -12840,7 +12840,7 @@
         <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>993550</v>
+        <v>1128400</v>
       </c>
       <c r="P89" t="n">
         <v>0</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
         <v>0</v>
       </c>
       <c r="N95" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="O95" t="n">
         <v>0</v>
@@ -13704,7 +13704,7 @@
         <v>0</v>
       </c>
       <c r="W95" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="X95" t="n">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>0</v>
       </c>
       <c r="AA95" t="n">
-        <v>150000</v>
+        <v>500000</v>
       </c>
       <c r="AB95" t="n">
         <v>5</v>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16757,7 +16757,7 @@
         <v>0</v>
       </c>
       <c r="N117" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="O117" t="n">
         <v>0</v>
@@ -16784,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="X117" t="n">
         <v>0</v>
@@ -16796,7 +16796,7 @@
         <v>0</v>
       </c>
       <c r="AA117" t="n">
-        <v>300000</v>
+        <v>450000</v>
       </c>
       <c r="AB117" t="n">
         <v>5</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
         <v>0</v>
       </c>
       <c r="N135" t="n">
-        <v>170000</v>
+        <v>270000</v>
       </c>
       <c r="O135" t="n">
         <v>100000</v>
@@ -19292,10 +19292,10 @@
         <v>170000</v>
       </c>
       <c r="S135" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="T135" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="U135" t="n">
         <v>170000</v>
@@ -19304,7 +19304,7 @@
         <v>0</v>
       </c>
       <c r="W135" t="n">
-        <v>170000</v>
+        <v>270000</v>
       </c>
       <c r="X135" t="n">
         <v>0</v>
@@ -19316,7 +19316,7 @@
         <v>0</v>
       </c>
       <c r="AA135" t="n">
-        <v>170000</v>
+        <v>270000</v>
       </c>
       <c r="AB135" t="n">
         <v>5</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19417,7 +19417,7 @@
         <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>235000</v>
+        <v>385000</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -19444,7 +19444,7 @@
         <v>0</v>
       </c>
       <c r="W136" t="n">
-        <v>235000</v>
+        <v>385000</v>
       </c>
       <c r="X136" t="n">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>0</v>
       </c>
       <c r="AA136" t="n">
-        <v>235000</v>
+        <v>385000</v>
       </c>
       <c r="AB136" t="n">
         <v>5</v>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20251,7 +20251,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>7207451.3</v>
+        <v>8034136.5</v>
       </c>
       <c r="M142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -26992,10 +26992,10 @@
         <v>5642757.56</v>
       </c>
       <c r="S190" t="n">
-        <v>2470271.07</v>
+        <v>2482175.87</v>
       </c>
       <c r="T190" t="n">
-        <v>2574618.83</v>
+        <v>2586523.63</v>
       </c>
       <c r="U190" t="n">
         <v>3325758.91</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
         <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>13774.95</v>
+        <v>15742.8</v>
       </c>
       <c r="P192" t="n">
         <v>0</v>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>
@@ -32023,22 +32023,22 @@
         <v>36382287.88</v>
       </c>
       <c r="P226" t="n">
-        <v>7296374.48</v>
+        <v>7725132.48</v>
       </c>
       <c r="Q226" t="n">
         <v>0</v>
       </c>
       <c r="R226" t="n">
-        <v>50222242.91</v>
+        <v>50574758.91</v>
       </c>
       <c r="S226" t="n">
-        <v>39557476.52</v>
+        <v>39909992.52</v>
       </c>
       <c r="T226" t="n">
-        <v>41170240.68</v>
+        <v>41522756.68</v>
       </c>
       <c r="U226" t="n">
-        <v>42925868.43</v>
+        <v>42849626.43</v>
       </c>
       <c r="V226" t="n">
         <v>1612764.16</v>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>14/09/2026 12:59:26</t>
+          <t>15/09/2026 11:29:53</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>79745.89</v>
+        <v>80600.89</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1232,10 +1232,10 @@
         <v>228261.29</v>
       </c>
       <c r="S6" t="n">
-        <v>79745.89</v>
+        <v>80600.89</v>
       </c>
       <c r="T6" t="n">
-        <v>96171.98</v>
+        <v>97026.98</v>
       </c>
       <c r="U6" t="n">
         <v>203353</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>172534.41</v>
+        <v>184675.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>105000</v>
       </c>
       <c r="W7" t="n">
-        <v>661845</v>
+        <v>648733</v>
       </c>
       <c r="X7" t="n">
         <v>327711</v>
@@ -1393,10 +1393,10 @@
         <v>63262</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>13112</v>
       </c>
       <c r="AA7" t="n">
-        <v>661845</v>
+        <v>648733</v>
       </c>
       <c r="AB7" t="n">
         <v>5</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1771,16 +1771,16 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5476636.35</v>
+        <v>5505051.35</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>295928.97</v>
+        <v>396040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>4789607.38</v>
+        <v>5070087.82</v>
       </c>
       <c r="P10" t="n">
         <v>9007845.380000001</v>
@@ -1789,7 +1789,7 @@
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>20960210.72</v>
+        <v>21060322.64</v>
       </c>
       <c r="S10" t="n">
         <v>10560541.59</v>
@@ -1798,13 +1798,13 @@
         <v>12143306.26</v>
       </c>
       <c r="U10" t="n">
-        <v>11952365.34</v>
+        <v>12052477.26</v>
       </c>
       <c r="V10" t="n">
         <v>1582764.67</v>
       </c>
       <c r="W10" t="n">
-        <v>11952587.12</v>
+        <v>12052699.12</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1816,7 +1816,7 @@
         <v>3887993.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>11982993.23</v>
+        <v>12083105.23</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>165003.57</v>
+        <v>172447.81</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1028688.4</v>
+        <v>1185724.86</v>
       </c>
       <c r="P18" t="n">
         <v>26813.15</v>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3171,7 +3171,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3516525.19</v>
+        <v>3552607.04</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3183,25 +3183,25 @@
         <v>3509598.53</v>
       </c>
       <c r="P20" t="n">
-        <v>4312664.33</v>
+        <v>4557916.3</v>
       </c>
       <c r="Q20" t="n">
         <v>316899.89</v>
       </c>
       <c r="R20" t="n">
-        <v>10318646.26</v>
+        <v>10565460.19</v>
       </c>
       <c r="S20" t="n">
-        <v>5436742.02</v>
+        <v>5982058.26</v>
       </c>
       <c r="T20" t="n">
-        <v>5585658.05</v>
+        <v>6351244.21</v>
       </c>
       <c r="U20" t="n">
-        <v>6005981.93</v>
+        <v>6007543.89</v>
       </c>
       <c r="V20" t="n">
-        <v>148916.03</v>
+        <v>369185.95</v>
       </c>
       <c r="W20" t="n">
         <v>6007543.89</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1304810.37</v>
+        <v>1305338.45</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,22 +4580,22 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1147094.82</v>
+        <v>1148279.86</v>
       </c>
       <c r="P30" t="n">
-        <v>657930.84</v>
+        <v>687082.77</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2760652.17</v>
+        <v>2789804.1</v>
       </c>
       <c r="S30" t="n">
-        <v>1832828.73</v>
+        <v>1881619.46</v>
       </c>
       <c r="T30" t="n">
-        <v>1990019.51</v>
+        <v>2038810.24</v>
       </c>
       <c r="U30" t="n">
         <v>2102721.33</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2692507.2</v>
+        <v>2702416.24</v>
       </c>
       <c r="P31" t="n">
         <v>7011787.82</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10883086.71</v>
+        <v>10891475.45</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9491342.73</v>
+        <v>9792171.199999999</v>
       </c>
       <c r="P32" t="n">
         <v>6152628.09</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1911654.51</v>
+        <v>2164294.85</v>
       </c>
       <c r="M36" t="n">
         <v>0</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6400,7 @@
         <v>131526</v>
       </c>
       <c r="O43" t="n">
-        <v>10313.28</v>
+        <v>10641.28</v>
       </c>
       <c r="P43" t="n">
         <v>114195.48</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3093631.5</v>
+        <v>3103131.5</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>2718069.51</v>
+        <v>2730193.85</v>
       </c>
       <c r="P46" t="n">
         <v>17377529.65</v>
@@ -6829,7 +6829,7 @@
         <v>5379029</v>
       </c>
       <c r="R46" t="n">
-        <v>31629021.26</v>
+        <v>31629816.65</v>
       </c>
       <c r="S46" t="n">
         <v>5945729.44</v>
@@ -6838,7 +6838,7 @@
         <v>6446179</v>
       </c>
       <c r="U46" t="n">
-        <v>14251491.61</v>
+        <v>14252287</v>
       </c>
       <c r="V46" t="n">
         <v>500449.56</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
         <v>7363410.03</v>
       </c>
       <c r="P52" t="n">
-        <v>4589956.52</v>
+        <v>4937905.31</v>
       </c>
       <c r="Q52" t="n">
         <v>278000</v>
@@ -7672,16 +7672,16 @@
         <v>13892639.52</v>
       </c>
       <c r="S52" t="n">
-        <v>9291804.449999999</v>
+        <v>8943855.66</v>
       </c>
       <c r="T52" t="n">
         <v>11946013.18</v>
       </c>
       <c r="U52" t="n">
-        <v>9302683</v>
+        <v>8954734.210000001</v>
       </c>
       <c r="V52" t="n">
-        <v>2654208.73</v>
+        <v>3002157.52</v>
       </c>
       <c r="W52" t="n">
         <v>9302683</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -14952,10 +14952,10 @@
         <v>106235.82</v>
       </c>
       <c r="S104" t="n">
-        <v>76123.00999999999</v>
+        <v>88523.00999999999</v>
       </c>
       <c r="T104" t="n">
-        <v>76123.00999999999</v>
+        <v>88523.00999999999</v>
       </c>
       <c r="U104" t="n">
         <v>105000</v>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15080,7 +15080,7 @@
         <v>0</v>
       </c>
       <c r="O105" t="n">
-        <v>276820.97</v>
+        <v>286730.01</v>
       </c>
       <c r="P105" t="n">
         <v>150685.93</v>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17192,10 +17192,10 @@
         <v>300000</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="U120" t="n">
         <v>300000</v>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -19983,7 +19983,7 @@
         <v>8445809.92</v>
       </c>
       <c r="P140" t="n">
-        <v>6308343.92</v>
+        <v>8057923.6</v>
       </c>
       <c r="Q140" t="n">
         <v>0</v>
@@ -19998,7 +19998,7 @@
         <v>8445809.92</v>
       </c>
       <c r="U140" t="n">
-        <v>12675633</v>
+        <v>10926053.32</v>
       </c>
       <c r="V140" t="n">
         <v>0</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20272,10 +20272,10 @@
         <v>673242.65</v>
       </c>
       <c r="S142" t="n">
-        <v>3852</v>
+        <v>257559.6</v>
       </c>
       <c r="T142" t="n">
-        <v>3852</v>
+        <v>257559.6</v>
       </c>
       <c r="U142" t="n">
         <v>378632</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22071,7 +22071,7 @@
         </is>
       </c>
       <c r="L155" t="n">
-        <v>1462637.56</v>
+        <v>2374086.03</v>
       </c>
       <c r="M155" t="n">
         <v>0</v>
@@ -22080,7 +22080,7 @@
         <v>0</v>
       </c>
       <c r="O155" t="n">
-        <v>1451637.56</v>
+        <v>1453637.56</v>
       </c>
       <c r="P155" t="n">
         <v>16244437.91</v>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
         <v>0</v>
       </c>
       <c r="W158" t="n">
-        <v>135000</v>
+        <v>68000</v>
       </c>
       <c r="X158" t="n">
         <v>0</v>
@@ -22533,10 +22533,10 @@
         <v>0</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>67000</v>
       </c>
       <c r="AA158" t="n">
-        <v>135000</v>
+        <v>68000</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23760,7 +23760,7 @@
         <v>211572</v>
       </c>
       <c r="O167" t="n">
-        <v>1771091.44</v>
+        <v>1772047.84</v>
       </c>
       <c r="P167" t="n">
         <v>2794234.52</v>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25592,10 +25592,10 @@
         <v>230000</v>
       </c>
       <c r="S180" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="T180" t="n">
-        <v>0</v>
+        <v>230000</v>
       </c>
       <c r="U180" t="n">
         <v>230000</v>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26411,7 +26411,7 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="M186" t="n">
         <v>0</v>
@@ -26420,7 +26420,7 @@
         <v>712872.0600000001</v>
       </c>
       <c r="O186" t="n">
-        <v>250000</v>
+        <v>350000</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27004,7 +27004,7 @@
         <v>3532.21</v>
       </c>
       <c r="W190" t="n">
-        <v>252998</v>
+        <v>232998</v>
       </c>
       <c r="X190" t="n">
         <v>200000</v>
@@ -27013,10 +27013,10 @@
         <v>0</v>
       </c>
       <c r="Z190" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="AA190" t="n">
-        <v>252998</v>
+        <v>232998</v>
       </c>
       <c r="AB190" t="n">
         <v>5</v>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
         <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>774265.55</v>
+        <v>784174.59</v>
       </c>
       <c r="P192" t="n">
         <v>1760683.97</v>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>1625643.01</v>
+        <v>1625762.81</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>318270.87</v>
+        <v>318450.57</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29351,7 +29351,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>13600</v>
+        <v>26200</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
@@ -29369,16 +29369,16 @@
         <v>39738</v>
       </c>
       <c r="R207" t="n">
-        <v>48000</v>
+        <v>48700</v>
       </c>
       <c r="S207" t="n">
-        <v>36000</v>
+        <v>36700</v>
       </c>
       <c r="T207" t="n">
-        <v>36600</v>
+        <v>37300</v>
       </c>
       <c r="U207" t="n">
-        <v>36600</v>
+        <v>37300</v>
       </c>
       <c r="V207" t="n">
         <v>600</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29512,10 +29512,10 @@
         <v>95090.62</v>
       </c>
       <c r="S208" t="n">
-        <v>0</v>
+        <v>42280.65</v>
       </c>
       <c r="T208" t="n">
-        <v>0</v>
+        <v>42280.65</v>
       </c>
       <c r="U208" t="n">
         <v>75949.64999999999</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31031,7 +31031,7 @@
         </is>
       </c>
       <c r="L219" t="n">
-        <v>143118375.23</v>
+        <v>143214278.92</v>
       </c>
       <c r="M219" t="n">
         <v>0</v>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>140903898.46</v>
+        <v>140960629.86</v>
       </c>
       <c r="P219" t="n">
         <v>49808521.04</v>
@@ -31052,10 +31052,10 @@
         <v>215486986.5</v>
       </c>
       <c r="S219" t="n">
-        <v>163819531.01</v>
+        <v>164477226.56</v>
       </c>
       <c r="T219" t="n">
-        <v>169486907.25</v>
+        <v>170144602.8</v>
       </c>
       <c r="U219" t="n">
         <v>165678465.46</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31460,7 +31460,7 @@
         <v>0</v>
       </c>
       <c r="O222" t="n">
-        <v>71986213.70999999</v>
+        <v>74449783.70999999</v>
       </c>
       <c r="P222" t="n">
         <v>62818272</v>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>56835882.9</v>
+        <v>58633632.9</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
@@ -31600,7 +31600,7 @@
         <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>54893496.57</v>
+        <v>55047627.33</v>
       </c>
       <c r="P223" t="n">
         <v>50438263.91</v>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>
@@ -32583,22 +32583,22 @@
         <v>36646414.73</v>
       </c>
       <c r="P230" t="n">
-        <v>7725132.48</v>
+        <v>8210357.48</v>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>51004882.91</v>
+        <v>51504644.28</v>
       </c>
       <c r="S230" t="n">
-        <v>40168141.52</v>
+        <v>40701603.52</v>
       </c>
       <c r="T230" t="n">
-        <v>41780905.68</v>
+        <v>42314367.68</v>
       </c>
       <c r="U230" t="n">
-        <v>43279750.43</v>
+        <v>43294286.8</v>
       </c>
       <c r="V230" t="n">
         <v>1612764.16</v>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>16/09/2026 11:21:01</t>
+          <t>18/09/2026 10:41:41</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1211,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>80600.89</v>
+        <v>125857.95</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -1223,25 +1223,25 @@
         <v>79745.89</v>
       </c>
       <c r="P6" t="n">
-        <v>24908.29</v>
+        <v>70400.53999999999</v>
       </c>
       <c r="Q6" t="n">
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>228261.29</v>
+        <v>273518.35</v>
       </c>
       <c r="S6" t="n">
-        <v>80600.89</v>
+        <v>125857.95</v>
       </c>
       <c r="T6" t="n">
-        <v>97026.98</v>
+        <v>174776.29</v>
       </c>
       <c r="U6" t="n">
-        <v>203353</v>
+        <v>203117.81</v>
       </c>
       <c r="V6" t="n">
-        <v>16426.09</v>
+        <v>48918.34</v>
       </c>
       <c r="W6" t="n">
         <v>203353</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>172231.02</v>
+        <v>200936.59</v>
       </c>
       <c r="P9" t="n">
         <v>388846.6</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
         <v>396040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5070087.82</v>
+        <v>5250416.47</v>
       </c>
       <c r="P10" t="n">
         <v>9007845.380000001</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1148279.86</v>
+        <v>1303727.73</v>
       </c>
       <c r="P30" t="n">
         <v>687082.77</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4720,7 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>2702416.24</v>
+        <v>3141258.4</v>
       </c>
       <c r="P31" t="n">
         <v>7011787.82</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>10891475.45</v>
+        <v>11151483.38</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,7 +4860,7 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9792171.199999999</v>
+        <v>9933149.08</v>
       </c>
       <c r="P32" t="n">
         <v>6152628.09</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>469627.74</v>
+        <v>523445.78</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>436865.44</v>
+        <v>468003.88</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
         <v>93886</v>
       </c>
       <c r="O46" t="n">
-        <v>2730193.85</v>
+        <v>2991441.23</v>
       </c>
       <c r="P46" t="n">
         <v>17377529.65</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7800,7 @@
         <v>217009.89</v>
       </c>
       <c r="O53" t="n">
-        <v>133073.4</v>
+        <v>155252.3</v>
       </c>
       <c r="P53" t="n">
         <v>163921.91</v>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11720,7 +11720,7 @@
         <v>537575.15</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>439634</v>
       </c>
       <c r="P81" t="n">
         <v>0</v>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14380,7 +14380,7 @@
         <v>22092.87</v>
       </c>
       <c r="O100" t="n">
-        <v>0</v>
+        <v>22092.87</v>
       </c>
       <c r="P100" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15220,7 +15220,7 @@
         <v>0</v>
       </c>
       <c r="O106" t="n">
-        <v>114042.91</v>
+        <v>114466.75</v>
       </c>
       <c r="P106" t="n">
         <v>260024.05</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
         <v>72910.97</v>
       </c>
       <c r="O113" t="n">
-        <v>39157.62</v>
+        <v>45683.89</v>
       </c>
       <c r="P113" t="n">
         <v>120156.43</v>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17332,10 +17332,10 @@
         <v>200000</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="U121" t="n">
         <v>200000</v>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22360,7 +22360,7 @@
         <v>0</v>
       </c>
       <c r="O157" t="n">
-        <v>39514.57</v>
+        <v>46040.84</v>
       </c>
       <c r="P157" t="n">
         <v>0</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22640,7 +22640,7 @@
         <v>234940.86</v>
       </c>
       <c r="O159" t="n">
-        <v>172231.02</v>
+        <v>200936.19</v>
       </c>
       <c r="P159" t="n">
         <v>189359.94</v>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22780,7 +22780,7 @@
         <v>190000</v>
       </c>
       <c r="O160" t="n">
-        <v>236546.44</v>
+        <v>237363.41</v>
       </c>
       <c r="P160" t="n">
         <v>348715.49</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26152,10 +26152,10 @@
         <v>261000</v>
       </c>
       <c r="S184" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="T184" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="U184" t="n">
         <v>261000</v>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
         <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>84789.60000000001</v>
+        <v>95912.85000000001</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27260,7 +27260,7 @@
         <v>0</v>
       </c>
       <c r="O192" t="n">
-        <v>784174.59</v>
+        <v>869016.0600000001</v>
       </c>
       <c r="P192" t="n">
         <v>1760683.97</v>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
         <v>0</v>
       </c>
       <c r="O193" t="n">
-        <v>1573472.63</v>
+        <v>1625643.01</v>
       </c>
       <c r="P193" t="n">
         <v>2316998.65</v>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29351,7 +29351,7 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>26200</v>
+        <v>29000</v>
       </c>
       <c r="M207" t="n">
         <v>0</v>
@@ -29369,7 +29369,7 @@
         <v>39738</v>
       </c>
       <c r="R207" t="n">
-        <v>48700</v>
+        <v>50100</v>
       </c>
       <c r="S207" t="n">
         <v>36700</v>
@@ -29378,7 +29378,7 @@
         <v>37300</v>
       </c>
       <c r="U207" t="n">
-        <v>37300</v>
+        <v>38700</v>
       </c>
       <c r="V207" t="n">
         <v>600</v>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31040,7 +31040,7 @@
         <v>0</v>
       </c>
       <c r="O219" t="n">
-        <v>140960629.86</v>
+        <v>143118375.23</v>
       </c>
       <c r="P219" t="n">
         <v>49808521.04</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31600,7 +31600,7 @@
         <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>55047627.33</v>
+        <v>55125882.9</v>
       </c>
       <c r="P223" t="n">
         <v>50438263.91</v>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -31880,7 +31880,7 @@
         <v>1406720</v>
       </c>
       <c r="O225" t="n">
-        <v>784000</v>
+        <v>907561.39</v>
       </c>
       <c r="P225" t="n">
         <v>0</v>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>
@@ -32583,22 +32583,22 @@
         <v>36646414.73</v>
       </c>
       <c r="P230" t="n">
-        <v>8210357.48</v>
+        <v>8216184.31</v>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
       </c>
       <c r="R230" t="n">
-        <v>51504644.28</v>
+        <v>51616608.25</v>
       </c>
       <c r="S230" t="n">
-        <v>40701603.52</v>
+        <v>40707430.35</v>
       </c>
       <c r="T230" t="n">
-        <v>42314367.68</v>
+        <v>42320194.51</v>
       </c>
       <c r="U230" t="n">
-        <v>43294286.8</v>
+        <v>43400423.94</v>
       </c>
       <c r="V230" t="n">
         <v>1612764.16</v>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>18/09/2026 10:41:41</t>
+          <t>20/09/2026 10:40:16</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>20/09/2026 10:40:16</t>
+          <t>21/09/2026 13:03:57</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1223,19 +1223,19 @@
         <v>79745.89</v>
       </c>
       <c r="P6" t="n">
-        <v>70400.53999999999</v>
+        <v>78988.2</v>
       </c>
       <c r="Q6" t="n">
         <v>46024</v>
       </c>
       <c r="R6" t="n">
-        <v>273518.35</v>
+        <v>282106.01</v>
       </c>
       <c r="S6" t="n">
-        <v>125857.95</v>
+        <v>134445.61</v>
       </c>
       <c r="T6" t="n">
-        <v>174776.29</v>
+        <v>183363.95</v>
       </c>
       <c r="U6" t="n">
         <v>203117.81</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>163512.81</v>
       </c>
       <c r="P7" t="n">
-        <v>462405.59</v>
+        <v>463005.59</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>1110619.55</v>
+        <v>1111166.16</v>
       </c>
       <c r="S7" t="n">
         <v>460484.87</v>
@@ -1378,7 +1378,7 @@
         <v>565484.87</v>
       </c>
       <c r="U7" t="n">
-        <v>648213.96</v>
+        <v>648160.5699999999</v>
       </c>
       <c r="V7" t="n">
         <v>105000</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>142145.4</v>
+        <v>142345.15</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1771,25 +1771,25 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5505051.35</v>
+        <v>5564940.83</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>396040.97</v>
+        <v>481040.97</v>
       </c>
       <c r="O10" t="n">
         <v>5250416.47</v>
       </c>
       <c r="P10" t="n">
-        <v>9007845.380000001</v>
+        <v>9092214.84</v>
       </c>
       <c r="Q10" t="n">
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>21060322.64</v>
+        <v>21229061.56</v>
       </c>
       <c r="S10" t="n">
         <v>10560541.59</v>
@@ -1798,13 +1798,13 @@
         <v>12143306.26</v>
       </c>
       <c r="U10" t="n">
-        <v>12052477.26</v>
+        <v>12136846.72</v>
       </c>
       <c r="V10" t="n">
         <v>1582764.67</v>
       </c>
       <c r="W10" t="n">
-        <v>12052699.12</v>
+        <v>12137699.12</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1816,7 +1816,7 @@
         <v>3887993.74</v>
       </c>
       <c r="AA10" t="n">
-        <v>12083105.23</v>
+        <v>12168105.23</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>88366.42</v>
+        <v>91903.95</v>
       </c>
       <c r="S17" t="n">
         <v>69900.72</v>
@@ -2778,7 +2778,7 @@
         <v>69900.72</v>
       </c>
       <c r="U17" t="n">
-        <v>78357.5</v>
+        <v>81895.03</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1305338.45</v>
+        <v>1306469.2</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4592,10 +4592,10 @@
         <v>2789804.1</v>
       </c>
       <c r="S30" t="n">
-        <v>1881619.46</v>
+        <v>1893306.06</v>
       </c>
       <c r="T30" t="n">
-        <v>2038810.24</v>
+        <v>2050496.84</v>
       </c>
       <c r="U30" t="n">
         <v>2102721.33</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11151483.38</v>
+        <v>11151770.22</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5131,7 +5131,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>98254.77</v>
+        <v>112525.09</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5420,7 +5420,7 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1911654.51</v>
+        <v>2164294.85</v>
       </c>
       <c r="P36" t="n">
         <v>2931914.44</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6409,7 +6409,7 @@
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>342938.94</v>
+        <v>344077.17</v>
       </c>
       <c r="S43" t="n">
         <v>114323.37</v>
@@ -6418,7 +6418,7 @@
         <v>118259.37</v>
       </c>
       <c r="U43" t="n">
-        <v>228743.46</v>
+        <v>229881.69</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3103131.5</v>
+        <v>3126069.55</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
         <v>3002157.52</v>
       </c>
       <c r="W52" t="n">
-        <v>9302683</v>
+        <v>8954734.210000001</v>
       </c>
       <c r="X52" t="n">
         <v>10590662</v>
@@ -7693,10 +7693,10 @@
         <v>1565979</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>347948.79</v>
       </c>
       <c r="AA52" t="n">
-        <v>10590662</v>
+        <v>10242713.21</v>
       </c>
       <c r="AB52" t="n">
         <v>5</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12271,7 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="M85" t="n">
         <v>0</v>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13272,10 +13272,10 @@
         <v>99996</v>
       </c>
       <c r="S92" t="n">
-        <v>0</v>
+        <v>99996</v>
       </c>
       <c r="T92" t="n">
-        <v>0</v>
+        <v>99996</v>
       </c>
       <c r="U92" t="n">
         <v>99996</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15211,7 +15211,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>114466.75</v>
+        <v>114535.85</v>
       </c>
       <c r="M106" t="n">
         <v>0</v>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20004,7 +20004,7 @@
         <v>0</v>
       </c>
       <c r="W140" t="n">
-        <v>12675633</v>
+        <v>10926053.32</v>
       </c>
       <c r="X140" t="n">
         <v>12675633</v>
@@ -20013,10 +20013,10 @@
         <v>0</v>
       </c>
       <c r="Z140" t="n">
-        <v>0</v>
+        <v>1749579.68</v>
       </c>
       <c r="AA140" t="n">
-        <v>12675633</v>
+        <v>10926053.32</v>
       </c>
       <c r="AB140" t="n">
         <v>5</v>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>237363.41</v>
+        <v>238532.09</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22783,13 +22783,13 @@
         <v>237363.41</v>
       </c>
       <c r="P160" t="n">
-        <v>348715.49</v>
+        <v>350343.49</v>
       </c>
       <c r="Q160" t="n">
         <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>774707.3</v>
+        <v>776334.78</v>
       </c>
       <c r="S160" t="n">
         <v>407247.39</v>
@@ -22798,7 +22798,7 @@
         <v>490977.01</v>
       </c>
       <c r="U160" t="n">
-        <v>425991.81</v>
+        <v>425991.29</v>
       </c>
       <c r="V160" t="n">
         <v>83729.62</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1773004.24</v>
+        <v>1773211.54</v>
       </c>
       <c r="M167" t="n">
         <v>0</v>
@@ -23769,7 +23769,7 @@
         <v>324976</v>
       </c>
       <c r="R167" t="n">
-        <v>6657461.87</v>
+        <v>6659918.53</v>
       </c>
       <c r="S167" t="n">
         <v>2878721.84</v>
@@ -23778,13 +23778,13 @@
         <v>3022364.72</v>
       </c>
       <c r="U167" t="n">
-        <v>3863227.35</v>
+        <v>3865684.01</v>
       </c>
       <c r="V167" t="n">
         <v>143642.88</v>
       </c>
       <c r="W167" t="n">
-        <v>3950828.72</v>
+        <v>3865828.72</v>
       </c>
       <c r="X167" t="n">
         <v>4953156</v>
@@ -23793,10 +23793,10 @@
         <v>324976.28</v>
       </c>
       <c r="Z167" t="n">
-        <v>1213899</v>
+        <v>1298899</v>
       </c>
       <c r="AA167" t="n">
-        <v>3950829</v>
+        <v>3865829</v>
       </c>
       <c r="AB167" t="n">
         <v>5</v>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25431,7 +25431,7 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M179" t="n">
         <v>0</v>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -25851,7 +25851,7 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="M182" t="n">
         <v>0</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26131,7 +26131,7 @@
         </is>
       </c>
       <c r="L184" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M184" t="n">
         <v>0</v>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -26837,7 +26837,7 @@
         <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2800000</v>
+        <v>4897528.47</v>
       </c>
       <c r="O189" t="n">
         <v>24545612.47</v>
@@ -26864,7 +26864,7 @@
         <v>667014.2</v>
       </c>
       <c r="W189" t="n">
-        <v>25226358</v>
+        <v>27323886.47</v>
       </c>
       <c r="X189" t="n">
         <v>22426358</v>
@@ -26876,7 +26876,7 @@
         <v>0</v>
       </c>
       <c r="AA189" t="n">
-        <v>25226358</v>
+        <v>27323886.47</v>
       </c>
       <c r="AB189" t="n">
         <v>5</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>318450.57</v>
+        <v>318485.12</v>
       </c>
       <c r="M204" t="n">
         <v>0</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30191,7 +30191,7 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="M213" t="n">
         <v>0</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31451,7 +31451,7 @@
         </is>
       </c>
       <c r="L222" t="n">
-        <v>76878033.70999999</v>
+        <v>79306283.70999999</v>
       </c>
       <c r="M222" t="n">
         <v>0</v>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31591,7 +31591,7 @@
         </is>
       </c>
       <c r="L223" t="n">
-        <v>58633632.9</v>
+        <v>61063632.9</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>
@@ -32571,7 +32571,7 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>36646414.73</v>
+        <v>37249300.96</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>21/09/2026 13:03:57</t>
+          <t>22/09/2026 11:08:50</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>79745.89</v>
+        <v>125857.95</v>
       </c>
       <c r="P6" t="n">
         <v>78988.2</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>184675.41</v>
+        <v>219675.41</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -1360,7 +1360,7 @@
         <v>334134</v>
       </c>
       <c r="O7" t="n">
-        <v>170379.41</v>
+        <v>179339.41</v>
       </c>
       <c r="P7" t="n">
         <v>463005.59</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5572094.86</v>
+        <v>5685376.71</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,22 +1780,22 @@
         <v>481040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5250416.47</v>
+        <v>5259030.87</v>
       </c>
       <c r="P10" t="n">
-        <v>9241883.289999999</v>
+        <v>9255039.300000001</v>
       </c>
       <c r="Q10" t="n">
         <v>3096601.89</v>
       </c>
       <c r="R10" t="n">
-        <v>21377582.53</v>
+        <v>21390738.54</v>
       </c>
       <c r="S10" t="n">
-        <v>10610322.79</v>
+        <v>10746602.21</v>
       </c>
       <c r="T10" t="n">
-        <v>12193087.46</v>
+        <v>12329366.88</v>
       </c>
       <c r="U10" t="n">
         <v>12135699.24</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>209528.86</v>
+        <v>209678.86</v>
       </c>
       <c r="M11" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
         <v>197487</v>
       </c>
       <c r="O11" t="n">
-        <v>172447.81</v>
+        <v>207299.27</v>
       </c>
       <c r="P11" t="n">
         <v>200450</v>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2763,13 +2763,13 @@
         <v>69900.72</v>
       </c>
       <c r="P17" t="n">
-        <v>10008.92</v>
+        <v>13890.58</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>91903.95</v>
+        <v>97816.95</v>
       </c>
       <c r="S17" t="n">
         <v>71840.72</v>
@@ -2778,7 +2778,7 @@
         <v>71840.72</v>
       </c>
       <c r="U17" t="n">
-        <v>81895.03</v>
+        <v>83926.37</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4011,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>10570590.51</v>
+        <v>11823903.46</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -4029,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>10572095.77</v>
+        <v>11825408.72</v>
       </c>
       <c r="S26" t="n">
-        <v>10572095.77</v>
+        <v>11825408.72</v>
       </c>
       <c r="T26" t="n">
-        <v>10572095.77</v>
+        <v>11825408.72</v>
       </c>
       <c r="U26" t="n">
-        <v>10572095.77</v>
+        <v>11825408.72</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4151,7 +4151,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4169,16 +4169,16 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="S27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="T27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="U27" t="n">
-        <v>3512.26</v>
+        <v>30832.63</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>175007.08</v>
+        <v>255571.15</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1306728.76</v>
+        <v>1307954.61</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -4580,25 +4580,25 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1304810.37</v>
+        <v>1305338.45</v>
       </c>
       <c r="P30" t="n">
-        <v>687082.77</v>
+        <v>687267.77</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2789804.1</v>
+        <v>2789986.81</v>
       </c>
       <c r="S30" t="n">
-        <v>1893306.06</v>
+        <v>1914306.06</v>
       </c>
       <c r="T30" t="n">
-        <v>2050496.84</v>
+        <v>2071496.84</v>
       </c>
       <c r="U30" t="n">
-        <v>2102721.33</v>
+        <v>2102719.04</v>
       </c>
       <c r="V30" t="n">
         <v>157190.78</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11180649.35</v>
+        <v>11564137.16</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,16 +4860,16 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>9936569.529999999</v>
+        <v>10197501.46</v>
       </c>
       <c r="P32" t="n">
-        <v>6152628.09</v>
+        <v>6153262.63</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>24832116.09</v>
+        <v>24832306.47</v>
       </c>
       <c r="S32" t="n">
         <v>18471298.29</v>
@@ -4878,7 +4878,7 @@
         <v>22254321.23</v>
       </c>
       <c r="U32" t="n">
-        <v>18679488</v>
+        <v>18679043.84</v>
       </c>
       <c r="V32" t="n">
         <v>3783022.94</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -4991,7 +4991,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>528055.76</v>
+        <v>528275.5699999999</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -5000,7 +5000,7 @@
         <v>110000</v>
       </c>
       <c r="O33" t="n">
-        <v>468003.88</v>
+        <v>521128.68</v>
       </c>
       <c r="P33" t="n">
         <v>12000</v>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -5289,16 +5289,16 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="S35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="T35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="U35" t="n">
-        <v>2986467.8</v>
+        <v>3360002.96</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3127284.86</v>
+        <v>3140108.86</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6832,10 +6832,10 @@
         <v>31629816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>5945729.44</v>
+        <v>5946524.83</v>
       </c>
       <c r="T46" t="n">
-        <v>6446179</v>
+        <v>6446974.39</v>
       </c>
       <c r="U46" t="n">
         <v>9701594.890000001</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6960,7 @@
         <v>219000</v>
       </c>
       <c r="O47" t="n">
-        <v>145554.86</v>
+        <v>182181.11</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8080,7 +8080,7 @@
         <v>50000</v>
       </c>
       <c r="O55" t="n">
-        <v>22561.87</v>
+        <v>24774.12</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13111,7 +13111,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1128400</v>
+        <v>1126850</v>
       </c>
       <c r="M91" t="n">
         <v>0</v>
@@ -13120,7 +13120,7 @@
         <v>0</v>
       </c>
       <c r="O91" t="n">
-        <v>1128400</v>
+        <v>1126850</v>
       </c>
       <c r="P91" t="n">
         <v>0</v>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14371,7 +14371,7 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="M100" t="n">
         <v>0</v>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15631,7 +15631,7 @@
         </is>
       </c>
       <c r="L109" t="n">
-        <v>114535.85</v>
+        <v>130683.3</v>
       </c>
       <c r="M109" t="n">
         <v>0</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15780,7 +15780,7 @@
         <v>40000</v>
       </c>
       <c r="O110" t="n">
-        <v>6643.05</v>
+        <v>7638.32</v>
       </c>
       <c r="P110" t="n">
         <v>450</v>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19131,7 +19131,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="M134" t="n">
         <v>0</v>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19271,7 +19271,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
+        <v>130000</v>
       </c>
       <c r="M135" t="n">
         <v>0</v>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19560,7 +19560,7 @@
         <v>400000</v>
       </c>
       <c r="O137" t="n">
-        <v>0</v>
+        <v>400000</v>
       </c>
       <c r="P137" t="n">
         <v>0</v>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20671,7 +20671,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>3647.37</v>
       </c>
       <c r="M145" t="n">
         <v>0</v>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22491,7 +22491,7 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>2476361.28</v>
+        <v>2505846.64</v>
       </c>
       <c r="M158" t="n">
         <v>0</v>
@@ -22500,7 +22500,7 @@
         <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>1453637.56</v>
+        <v>2365086.03</v>
       </c>
       <c r="P158" t="n">
         <v>16674823.21</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22771,7 +22771,7 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>46040.84</v>
+        <v>46107.45</v>
       </c>
       <c r="M160" t="n">
         <v>0</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23191,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>238532.09</v>
+        <v>271122.52</v>
       </c>
       <c r="M163" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23340,7 +23340,7 @@
         <v>50000</v>
       </c>
       <c r="O164" t="n">
-        <v>27866.98</v>
+        <v>30432.08</v>
       </c>
       <c r="P164" t="n">
         <v>2250</v>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1773211.54</v>
+        <v>1775260.31</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27120,7 +27120,7 @@
         <v>712872.0600000001</v>
       </c>
       <c r="O191" t="n">
-        <v>350000</v>
+        <v>452872.05</v>
       </c>
       <c r="P191" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27391,7 +27391,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>7108000</v>
+        <v>7107600</v>
       </c>
       <c r="M193" t="n">
         <v>0</v>
@@ -27400,7 +27400,7 @@
         <v>371000</v>
       </c>
       <c r="O193" t="n">
-        <v>7108000</v>
+        <v>7107600</v>
       </c>
       <c r="P193" t="n">
         <v>0</v>
@@ -27412,7 +27412,7 @@
         <v>9076439.67</v>
       </c>
       <c r="S193" t="n">
-        <v>7108000</v>
+        <v>7107600</v>
       </c>
       <c r="T193" t="n">
         <v>8061200</v>
@@ -27421,7 +27421,7 @@
         <v>9076439.67</v>
       </c>
       <c r="V193" t="n">
-        <v>953200</v>
+        <v>953600</v>
       </c>
       <c r="W193" t="n">
         <v>9076439.67</v>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27549,7 +27549,7 @@
         <v>0</v>
       </c>
       <c r="R194" t="n">
-        <v>27111664.26</v>
+        <v>28879142.9</v>
       </c>
       <c r="S194" t="n">
         <v>25225912.81</v>
@@ -27558,7 +27558,7 @@
         <v>25892927.01</v>
       </c>
       <c r="U194" t="n">
-        <v>25226358</v>
+        <v>26993836.64</v>
       </c>
       <c r="V194" t="n">
         <v>667014.2</v>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -27811,7 +27811,7 @@
         </is>
       </c>
       <c r="L196" t="n">
-        <v>95912.85000000001</v>
+        <v>97412.85000000001</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1652021.25</v>
+        <v>1709187.91</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30060,7 +30060,7 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>11500</v>
+        <v>24800</v>
       </c>
       <c r="P212" t="n">
         <v>11400</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31731,7 +31731,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>143327924.45</v>
+        <v>143354924.45</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
@@ -31743,25 +31743,25 @@
         <v>143214278.92</v>
       </c>
       <c r="P224" t="n">
-        <v>50235480.46</v>
+        <v>50430560.11</v>
       </c>
       <c r="Q224" t="n">
         <v>5086650.13</v>
       </c>
       <c r="R224" t="n">
-        <v>215486986.5</v>
+        <v>216144682.06</v>
       </c>
       <c r="S224" t="n">
-        <v>164050267.14</v>
+        <v>163960267.15</v>
       </c>
       <c r="T224" t="n">
-        <v>170144602.8</v>
+        <v>170144602.81</v>
       </c>
       <c r="U224" t="n">
-        <v>165251506.04</v>
+        <v>165714121.95</v>
       </c>
       <c r="V224" t="n">
-        <v>6094335.66</v>
+        <v>6184335.66</v>
       </c>
       <c r="W224" t="n">
         <v>165715582</v>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32291,7 +32291,7 @@
         </is>
       </c>
       <c r="L228" t="n">
-        <v>61551749.34</v>
+        <v>61764732.72</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -32300,28 +32300,28 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>56835882.9</v>
+        <v>58633632.9</v>
       </c>
       <c r="P228" t="n">
-        <v>50438263.91</v>
+        <v>51388595.59</v>
       </c>
       <c r="Q228" t="n">
         <v>0</v>
       </c>
       <c r="R228" t="n">
-        <v>129881289.91</v>
+        <v>130831621.59</v>
       </c>
       <c r="S228" t="n">
-        <v>79232487.98999999</v>
+        <v>78778260.98999999</v>
       </c>
       <c r="T228" t="n">
-        <v>99386487.98999999</v>
+        <v>99672054.66</v>
       </c>
       <c r="U228" t="n">
         <v>79443026</v>
       </c>
       <c r="V228" t="n">
-        <v>20154000</v>
+        <v>20893793.67</v>
       </c>
       <c r="W228" t="n">
         <v>79443026</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>
@@ -33271,7 +33271,7 @@
         </is>
       </c>
       <c r="L235" t="n">
-        <v>37249300.96</v>
+        <v>37255127.79</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -33289,7 +33289,7 @@
         <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>51616608.25</v>
+        <v>51905693.91</v>
       </c>
       <c r="S235" t="n">
         <v>41221083.35</v>
@@ -33298,7 +33298,7 @@
         <v>42833847.51</v>
       </c>
       <c r="U235" t="n">
-        <v>43259857.94</v>
+        <v>43548943.6</v>
       </c>
       <c r="V235" t="n">
         <v>1612764.16</v>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>24/09/2026 11:18:43</t>
+          <t>27/09/2026 11:53:27</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>27/09/2026 11:53:27</t>
+          <t>28/09/2026 14:44:47</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
         <v>84393.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>50000</v>
       </c>
       <c r="R4" t="n">
         <v>178086</v>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>93886</v>
+        <v>143886</v>
       </c>
       <c r="X4" t="n">
         <v>50000</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
         <v>78988.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>46024</v>
+        <v>48647</v>
       </c>
       <c r="R6" t="n">
         <v>282106.01</v>
@@ -1244,7 +1244,7 @@
         <v>48918.34</v>
       </c>
       <c r="W6" t="n">
-        <v>203353</v>
+        <v>205976</v>
       </c>
       <c r="X6" t="n">
         <v>252000</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1646,7 +1646,7 @@
         <v>388846.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>128044</v>
       </c>
       <c r="R9" t="n">
         <v>874689.4</v>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>485842.8</v>
+        <v>613886.8</v>
       </c>
       <c r="X9" t="n">
         <v>663294</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5685376.71</v>
+        <v>5689780.54</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>9255039.300000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>3096601.89</v>
+        <v>3127008</v>
       </c>
       <c r="R10" t="n">
         <v>21390738.54</v>
@@ -1804,7 +1804,7 @@
         <v>1582764.67</v>
       </c>
       <c r="W10" t="n">
-        <v>12137699.12</v>
+        <v>12168105.23</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>48261</v>
       </c>
       <c r="R13" t="n">
         <v>193219.94</v>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>201739</v>
+        <v>250000</v>
       </c>
       <c r="X13" t="n">
         <v>250000</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2766,7 +2766,7 @@
         <v>13890.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="R17" t="n">
         <v>97816.95</v>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>285000</v>
+        <v>300000</v>
       </c>
       <c r="X17" t="n">
         <v>300000</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
         <v>4557916.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>316899.89</v>
+        <v>1075689</v>
       </c>
       <c r="R20" t="n">
         <v>10565460.19</v>
@@ -3204,7 +3204,7 @@
         <v>369185.95</v>
       </c>
       <c r="W20" t="n">
-        <v>6007543.89</v>
+        <v>6766333</v>
       </c>
       <c r="X20" t="n">
         <v>6766333</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>21804</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2262.96</v>
+        <v>24066.96</v>
       </c>
       <c r="X23" t="n">
         <v>25698</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3746,7 +3746,7 @@
         <v>68464.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>50000</v>
+        <v>169694</v>
       </c>
       <c r="R24" t="n">
         <v>131343.68</v>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>80306</v>
+        <v>200000</v>
       </c>
       <c r="X24" t="n">
         <v>200000</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>24854</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>20844</v>
+        <v>45698</v>
       </c>
       <c r="X25" t="n">
         <v>45698</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4583,25 +4583,25 @@
         <v>1305338.45</v>
       </c>
       <c r="P30" t="n">
-        <v>687267.77</v>
+        <v>691083.77</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2789986.81</v>
+        <v>2791996.67</v>
       </c>
       <c r="S30" t="n">
-        <v>1914306.06</v>
+        <v>1914692.63</v>
       </c>
       <c r="T30" t="n">
-        <v>2071496.84</v>
+        <v>2073689.41</v>
       </c>
       <c r="U30" t="n">
-        <v>2102719.04</v>
+        <v>2100912.9</v>
       </c>
       <c r="V30" t="n">
-        <v>157190.78</v>
+        <v>158996.78</v>
       </c>
       <c r="W30" t="n">
         <v>2102736</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
         <v>7011787.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>36087</v>
       </c>
       <c r="R31" t="n">
         <v>14215932.82</v>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>7204145</v>
+        <v>7240232</v>
       </c>
       <c r="X31" t="n">
         <v>7240232</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -4866,25 +4866,25 @@
         <v>6153262.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>103049</v>
       </c>
       <c r="R32" t="n">
         <v>24832306.47</v>
       </c>
       <c r="S32" t="n">
-        <v>18471298.29</v>
+        <v>18489073.68</v>
       </c>
       <c r="T32" t="n">
-        <v>22254321.23</v>
+        <v>22274038.09</v>
       </c>
       <c r="U32" t="n">
         <v>18679043.84</v>
       </c>
       <c r="V32" t="n">
-        <v>3783022.94</v>
+        <v>3784964.41</v>
       </c>
       <c r="W32" t="n">
-        <v>18679488</v>
+        <v>18782537</v>
       </c>
       <c r="X32" t="n">
         <v>18370086</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5146,7 @@
         <v>226413.89</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>228955.89</v>
       </c>
       <c r="R34" t="n">
         <v>507458</v>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>281044.11</v>
+        <v>510000</v>
       </c>
       <c r="X34" t="n">
         <v>510000</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5426,7 +5426,7 @@
         <v>2931914.44</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>14953</v>
       </c>
       <c r="R36" t="n">
         <v>5916961.44</v>
@@ -5444,7 +5444,7 @@
         <v>28253.96</v>
       </c>
       <c r="W36" t="n">
-        <v>2985047</v>
+        <v>3000000</v>
       </c>
       <c r="X36" t="n">
         <v>3000000</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -5986,7 +5986,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="X40" t="n">
         <v>2000</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6552,10 +6552,10 @@
         <v>246992.57</v>
       </c>
       <c r="S44" t="n">
-        <v>68800</v>
+        <v>72380.13</v>
       </c>
       <c r="T44" t="n">
-        <v>68800</v>
+        <v>72380.13</v>
       </c>
       <c r="U44" t="n">
         <v>150000</v>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -6832,10 +6832,10 @@
         <v>31629816.65</v>
       </c>
       <c r="S46" t="n">
-        <v>5946524.83</v>
+        <v>5960845.37</v>
       </c>
       <c r="T46" t="n">
-        <v>6446974.39</v>
+        <v>6461294.93</v>
       </c>
       <c r="U46" t="n">
         <v>9701594.890000001</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>15037</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>86656</v>
+        <v>101693</v>
       </c>
       <c r="X54" t="n">
         <v>101693</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3646</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -8524,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>16354</v>
+        <v>20000</v>
       </c>
       <c r="X58" t="n">
         <v>20000</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
         <v>7507405.83</v>
       </c>
       <c r="Q59" t="n">
-        <v>1514015.72</v>
+        <v>4186869</v>
       </c>
       <c r="R59" t="n">
         <v>25835164.83</v>
@@ -8664,7 +8664,7 @@
         <v>5679708.17</v>
       </c>
       <c r="W59" t="n">
-        <v>18518759</v>
+        <v>21191612.28</v>
       </c>
       <c r="X59" t="n">
         <v>22965724</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -12846,7 +12846,7 @@
         <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>24203</v>
       </c>
       <c r="R89" t="n">
         <v>21050</v>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>25389</v>
+        <v>49592</v>
       </c>
       <c r="X89" t="n">
         <v>49592</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15506,7 +15506,7 @@
         <v>150685.93</v>
       </c>
       <c r="Q108" t="n">
-        <v>74157.22</v>
+        <v>246945</v>
       </c>
       <c r="R108" t="n">
         <v>840898.15</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>690212.22</v>
+        <v>863000</v>
       </c>
       <c r="X108" t="n">
         <v>863000</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15646,7 +15646,7 @@
         <v>260024.05</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>719080.22</v>
       </c>
       <c r="R109" t="n">
         <v>570236.66</v>
@@ -15664,7 +15664,7 @@
         <v>1350</v>
       </c>
       <c r="W109" t="n">
-        <v>355872.78</v>
+        <v>1074953</v>
       </c>
       <c r="X109" t="n">
         <v>1314953</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16486,7 +16486,7 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>10177</v>
       </c>
       <c r="R115" t="n">
         <v>30000</v>
@@ -16504,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>61773.4</v>
+        <v>71950.39999999999</v>
       </c>
       <c r="X115" t="n">
         <v>80000</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16766,7 +16766,7 @@
         <v>50000</v>
       </c>
       <c r="Q117" t="n">
-        <v>0</v>
+        <v>57248</v>
       </c>
       <c r="R117" t="n">
         <v>442635.02</v>
@@ -16784,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>392752</v>
+        <v>450000</v>
       </c>
       <c r="X117" t="n">
         <v>450000</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -17886,7 +17886,7 @@
         <v>0</v>
       </c>
       <c r="Q125" t="n">
-        <v>49471</v>
+        <v>99125.72</v>
       </c>
       <c r="R125" t="n">
         <v>345.28</v>
@@ -17904,7 +17904,7 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>345.28</v>
+        <v>50000</v>
       </c>
       <c r="X125" t="n">
         <v>50000</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18166,7 +18166,7 @@
         <v>2000</v>
       </c>
       <c r="Q127" t="n">
-        <v>49471</v>
+        <v>70413</v>
       </c>
       <c r="R127" t="n">
         <v>4600</v>
@@ -18184,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>26594.19</v>
+        <v>47536.19</v>
       </c>
       <c r="X127" t="n">
         <v>50000</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18306,7 +18306,7 @@
         <v>2000</v>
       </c>
       <c r="Q128" t="n">
-        <v>50000</v>
+        <v>1261000</v>
       </c>
       <c r="R128" t="n">
         <v>36599.31</v>
@@ -18324,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>42000</v>
+        <v>1253000</v>
       </c>
       <c r="X128" t="n">
         <v>1261000</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18586,7 @@
         <v>0</v>
       </c>
       <c r="Q130" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="R130" t="n">
         <v>0</v>
@@ -18604,7 +18604,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="X130" t="n">
         <v>550500</v>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -19849,7 +19849,7 @@
         <v>0</v>
       </c>
       <c r="R139" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="S139" t="n">
         <v>0</v>
@@ -19858,7 +19858,7 @@
         <v>0</v>
       </c>
       <c r="U139" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="V139" t="n">
         <v>0</v>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20111,7 +20111,7 @@
         </is>
       </c>
       <c r="L141" t="n">
-        <v>100000</v>
+        <v>170000</v>
       </c>
       <c r="M141" t="n">
         <v>0</v>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
         <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>0</v>
+        <v>2607835</v>
       </c>
       <c r="R148" t="n">
         <v>9748668.68</v>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>9813947</v>
+        <v>12421782</v>
       </c>
       <c r="X148" t="n">
         <v>12421782</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21246,7 +21246,7 @@
         <v>0</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="R149" t="n">
         <v>0</v>
@@ -21264,7 +21264,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="X149" t="n">
         <v>56000</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22366,7 +22366,7 @@
         <v>19046</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>24738</v>
       </c>
       <c r="R157" t="n">
         <v>39246</v>
@@ -22384,7 +22384,7 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>75262</v>
+        <v>100000</v>
       </c>
       <c r="X157" t="n">
         <v>100000</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22506,7 +22506,7 @@
         <v>16674823.21</v>
       </c>
       <c r="Q158" t="n">
-        <v>0</v>
+        <v>65000</v>
       </c>
       <c r="R158" t="n">
         <v>23880736.73</v>
@@ -22524,7 +22524,7 @@
         <v>11000</v>
       </c>
       <c r="W158" t="n">
-        <v>7639296</v>
+        <v>7704296</v>
       </c>
       <c r="X158" t="n">
         <v>8429440</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22786,7 +22786,7 @@
         <v>240000</v>
       </c>
       <c r="Q160" t="n">
-        <v>0</v>
+        <v>278000</v>
       </c>
       <c r="R160" t="n">
         <v>347516.39</v>
@@ -22804,7 +22804,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>385648</v>
+        <v>663648</v>
       </c>
       <c r="X160" t="n">
         <v>867556</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24046,7 +24046,7 @@
         <v>0</v>
       </c>
       <c r="Q169" t="n">
-        <v>0</v>
+        <v>27832</v>
       </c>
       <c r="R169" t="n">
         <v>1083437</v>
@@ -24064,7 +24064,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>1083437</v>
+        <v>1111269</v>
       </c>
       <c r="X169" t="n">
         <v>547269</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1775260.31</v>
+        <v>1809344.33</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25026,7 +25026,7 @@
         <v>0</v>
       </c>
       <c r="Q176" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="R176" t="n">
         <v>0</v>
@@ -25044,7 +25044,7 @@
         <v>0</v>
       </c>
       <c r="W176" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X176" t="n">
         <v>10000</v>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27412,10 +27412,10 @@
         <v>9076439.67</v>
       </c>
       <c r="S193" t="n">
-        <v>7107600</v>
+        <v>7935600</v>
       </c>
       <c r="T193" t="n">
-        <v>8061200</v>
+        <v>8889200</v>
       </c>
       <c r="U193" t="n">
         <v>9076439.67</v>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28106,7 +28106,7 @@
         <v>2763223.97</v>
       </c>
       <c r="Q198" t="n">
-        <v>0</v>
+        <v>65487</v>
       </c>
       <c r="R198" t="n">
         <v>6089210.8</v>
@@ -28124,7 +28124,7 @@
         <v>104347.76</v>
       </c>
       <c r="W198" t="n">
-        <v>3328090.03</v>
+        <v>3393577.03</v>
       </c>
       <c r="X198" t="n">
         <v>4806049</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28526,7 +28526,7 @@
         <v>0</v>
       </c>
       <c r="Q201" t="n">
-        <v>329000</v>
+        <v>330000</v>
       </c>
       <c r="R201" t="n">
         <v>0</v>
@@ -28544,7 +28544,7 @@
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="X201" t="n">
         <v>110000</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29506,7 +29506,7 @@
         <v>0</v>
       </c>
       <c r="Q208" t="n">
-        <v>0</v>
+        <v>69388</v>
       </c>
       <c r="R208" t="n">
         <v>80612</v>
@@ -29524,7 +29524,7 @@
         <v>0</v>
       </c>
       <c r="W208" t="n">
-        <v>80612</v>
+        <v>150000</v>
       </c>
       <c r="X208" t="n">
         <v>150000</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29646,7 +29646,7 @@
         <v>4837262.97</v>
       </c>
       <c r="Q209" t="n">
-        <v>5054381</v>
+        <v>5886824</v>
       </c>
       <c r="R209" t="n">
         <v>7758858.94</v>
@@ -29664,7 +29664,7 @@
         <v>1894229.63</v>
       </c>
       <c r="W209" t="n">
-        <v>4801538</v>
+        <v>5633981</v>
       </c>
       <c r="X209" t="n">
         <v>10925362</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30206,7 +30206,7 @@
         <v>19140.97</v>
       </c>
       <c r="Q213" t="n">
-        <v>0</v>
+        <v>187297</v>
       </c>
       <c r="R213" t="n">
         <v>95090.62</v>
@@ -30224,7 +30224,7 @@
         <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>111422</v>
+        <v>298719</v>
       </c>
       <c r="X213" t="n">
         <v>220966</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31046,7 +31046,7 @@
         <v>0</v>
       </c>
       <c r="Q219" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="R219" t="n">
         <v>0</v>
@@ -31064,7 +31064,7 @@
         <v>0</v>
       </c>
       <c r="W219" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="X219" t="n">
         <v>589773</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31746,7 +31746,7 @@
         <v>50430560.11</v>
       </c>
       <c r="Q224" t="n">
-        <v>5086650.13</v>
+        <v>5735947</v>
       </c>
       <c r="R224" t="n">
         <v>216144682.06</v>
@@ -31764,7 +31764,7 @@
         <v>6184335.66</v>
       </c>
       <c r="W224" t="n">
-        <v>165715582</v>
+        <v>166364878.87</v>
       </c>
       <c r="X224" t="n">
         <v>171813039</v>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32306,7 +32306,7 @@
         <v>51388595.59</v>
       </c>
       <c r="Q228" t="n">
-        <v>0</v>
+        <v>2792377</v>
       </c>
       <c r="R228" t="n">
         <v>130831621.59</v>
@@ -32324,7 +32324,7 @@
         <v>20893793.67</v>
       </c>
       <c r="W228" t="n">
-        <v>79443026</v>
+        <v>82235403</v>
       </c>
       <c r="X228" t="n">
         <v>83642123</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>28/09/2026 14:44:47</t>
+          <t>29/09/2026 12:52:47</t>
         </is>
       </c>
     </row>

--- a/base_despesas/2026/despesas_202609.xlsx
+++ b/base_despesas/2026/despesas_202609.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -874,7 +874,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>143886</v>
+        <v>93886</v>
       </c>
       <c r="X4" t="n">
         <v>50000</v>
@@ -973,10 +973,10 @@
         <v>50000</v>
       </c>
       <c r="Z4" t="n">
-        <v>34200</v>
+        <v>84200</v>
       </c>
       <c r="AA4" t="n">
-        <v>143886</v>
+        <v>93886</v>
       </c>
       <c r="AB4" t="n">
         <v>5</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
         <v>48918.34</v>
       </c>
       <c r="W6" t="n">
-        <v>205976</v>
+        <v>203353</v>
       </c>
       <c r="X6" t="n">
         <v>252000</v>
@@ -1253,10 +1253,10 @@
         <v>48647</v>
       </c>
       <c r="Z6" t="n">
-        <v>46024</v>
+        <v>48647</v>
       </c>
       <c r="AA6" t="n">
-        <v>205976</v>
+        <v>203353</v>
       </c>
       <c r="AB6" t="n">
         <v>5</v>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>179339.41</v>
       </c>
       <c r="P7" t="n">
-        <v>463005.59</v>
+        <v>484516.99</v>
       </c>
       <c r="Q7" t="n">
         <v>63262</v>
       </c>
       <c r="R7" t="n">
-        <v>1111166.16</v>
+        <v>1132677.56</v>
       </c>
       <c r="S7" t="n">
         <v>460484.87</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1664,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>613886.8</v>
+        <v>485842.8</v>
       </c>
       <c r="X9" t="n">
         <v>663294</v>
@@ -1673,10 +1673,10 @@
         <v>128044</v>
       </c>
       <c r="Z9" t="n">
-        <v>49407.2</v>
+        <v>177451.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>613886.8</v>
+        <v>485842.8</v>
       </c>
       <c r="AB9" t="n">
         <v>5</v>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1771,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>5689780.54</v>
+        <v>5682766.01</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -1780,10 +1780,10 @@
         <v>481040.97</v>
       </c>
       <c r="O10" t="n">
-        <v>5259030.87</v>
+        <v>5272096.36</v>
       </c>
       <c r="P10" t="n">
-        <v>9255039.300000001</v>
+        <v>9266345.300000001</v>
       </c>
       <c r="Q10" t="n">
         <v>3127008</v>
@@ -1792,19 +1792,19 @@
         <v>21390738.54</v>
       </c>
       <c r="S10" t="n">
-        <v>10746602.21</v>
+        <v>10830165.67</v>
       </c>
       <c r="T10" t="n">
-        <v>12329366.88</v>
+        <v>12424236.34</v>
       </c>
       <c r="U10" t="n">
-        <v>12135699.24</v>
+        <v>12124393.24</v>
       </c>
       <c r="V10" t="n">
-        <v>1582764.67</v>
+        <v>1594070.67</v>
       </c>
       <c r="W10" t="n">
-        <v>12168105.23</v>
+        <v>12137699.12</v>
       </c>
       <c r="X10" t="n">
         <v>15575058</v>
@@ -1813,10 +1813,10 @@
         <v>3127008</v>
       </c>
       <c r="Z10" t="n">
-        <v>3887993.74</v>
+        <v>3918399.85</v>
       </c>
       <c r="AA10" t="n">
-        <v>12168105.23</v>
+        <v>12137699.12</v>
       </c>
       <c r="AB10" t="n">
         <v>5</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>250000</v>
+        <v>201739</v>
       </c>
       <c r="X13" t="n">
         <v>250000</v>
@@ -2233,10 +2233,10 @@
         <v>48261</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>48261</v>
       </c>
       <c r="AA13" t="n">
-        <v>250000</v>
+        <v>201739</v>
       </c>
       <c r="AB13" t="n">
         <v>5</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>300000</v>
+        <v>285000</v>
       </c>
       <c r="X17" t="n">
         <v>300000</v>
@@ -2793,10 +2793,10 @@
         <v>15000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="AA17" t="n">
-        <v>300000</v>
+        <v>285000</v>
       </c>
       <c r="AB17" t="n">
         <v>5</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2974,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
         <v>369185.95</v>
       </c>
       <c r="W20" t="n">
-        <v>6766333</v>
+        <v>6007543.89</v>
       </c>
       <c r="X20" t="n">
         <v>6766333</v>
@@ -3213,10 +3213,10 @@
         <v>1075689</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>758789.11</v>
       </c>
       <c r="AA20" t="n">
-        <v>6766333</v>
+        <v>6007543.89</v>
       </c>
       <c r="AB20" t="n">
         <v>5</v>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3534,7 +3534,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>24066.96</v>
+        <v>2262.96</v>
       </c>
       <c r="X23" t="n">
         <v>25698</v>
@@ -3633,10 +3633,10 @@
         <v>21804</v>
       </c>
       <c r="Z23" t="n">
-        <v>1631.04</v>
+        <v>23435.04</v>
       </c>
       <c r="AA23" t="n">
-        <v>24066.96</v>
+        <v>2262.96</v>
       </c>
       <c r="AB23" t="n">
         <v>5</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3764,7 +3764,7 @@
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>200000</v>
+        <v>80306</v>
       </c>
       <c r="X24" t="n">
         <v>200000</v>
@@ -3773,10 +3773,10 @@
         <v>169694</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>119694</v>
       </c>
       <c r="AA24" t="n">
-        <v>200000</v>
+        <v>80306</v>
       </c>
       <c r="AB24" t="n">
         <v>5</v>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>45698</v>
+        <v>20844</v>
       </c>
       <c r="X25" t="n">
         <v>45698</v>
@@ -3913,10 +3913,10 @@
         <v>24854</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>24854</v>
       </c>
       <c r="AA25" t="n">
-        <v>45698</v>
+        <v>20844</v>
       </c>
       <c r="AB25" t="n">
         <v>5</v>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4580,22 +4580,22 @@
         <v>261000</v>
       </c>
       <c r="O30" t="n">
-        <v>1305338.45</v>
+        <v>1306469.2</v>
       </c>
       <c r="P30" t="n">
-        <v>691083.77</v>
+        <v>691663.77</v>
       </c>
       <c r="Q30" t="n">
         <v>9180</v>
       </c>
       <c r="R30" t="n">
-        <v>2791996.67</v>
+        <v>2792576.67</v>
       </c>
       <c r="S30" t="n">
-        <v>1914692.63</v>
+        <v>1915272.63</v>
       </c>
       <c r="T30" t="n">
-        <v>2073689.41</v>
+        <v>2074269.41</v>
       </c>
       <c r="U30" t="n">
         <v>2100912.9</v>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4744,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>7240232</v>
+        <v>7204145</v>
       </c>
       <c r="X31" t="n">
         <v>7240232</v>
@@ -4753,10 +4753,10 @@
         <v>36087</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>36087</v>
       </c>
       <c r="AA31" t="n">
-        <v>7240232</v>
+        <v>7204145</v>
       </c>
       <c r="AB31" t="n">
         <v>5</v>
@@ -4794,7 +4794,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>11564137.16</v>
+        <v>11564529.15</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -4860,10 +4860,10 @@
         <v>725144</v>
       </c>
       <c r="O32" t="n">
-        <v>10197501.46</v>
+        <v>10197788.3</v>
       </c>
       <c r="P32" t="n">
-        <v>6153262.63</v>
+        <v>6155204.1</v>
       </c>
       <c r="Q32" t="n">
         <v>103049</v>
@@ -4878,13 +4878,13 @@
         <v>22274038.09</v>
       </c>
       <c r="U32" t="n">
-        <v>18679043.84</v>
+        <v>18677102.37</v>
       </c>
       <c r="V32" t="n">
         <v>3784964.41</v>
       </c>
       <c r="W32" t="n">
-        <v>18782537</v>
+        <v>18679488</v>
       </c>
       <c r="X32" t="n">
         <v>18370086</v>
@@ -4893,10 +4893,10 @@
         <v>103049</v>
       </c>
       <c r="Z32" t="n">
-        <v>312693</v>
+        <v>415742</v>
       </c>
       <c r="AA32" t="n">
-        <v>18782537</v>
+        <v>18679488</v>
       </c>
       <c r="AB32" t="n">
         <v>5</v>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5074,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
         <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>510000</v>
+        <v>281044.11</v>
       </c>
       <c r="X34" t="n">
         <v>510000</v>
@@ -5173,10 +5173,10 @@
         <v>228955.89</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>228955.89</v>
       </c>
       <c r="AA34" t="n">
-        <v>510000</v>
+        <v>281044.11</v>
       </c>
       <c r="AB34" t="n">
         <v>5</v>
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5354,7 +5354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
         <v>28253.96</v>
       </c>
       <c r="W36" t="n">
-        <v>3000000</v>
+        <v>2985047</v>
       </c>
       <c r="X36" t="n">
         <v>3000000</v>
@@ -5453,10 +5453,10 @@
         <v>14953</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>14953</v>
       </c>
       <c r="AA36" t="n">
-        <v>3000000</v>
+        <v>2985047</v>
       </c>
       <c r="AB36" t="n">
         <v>5</v>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>2000</v>
@@ -6013,10 +6013,10 @@
         <v>2000</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="AA40" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>5</v>
@@ -6054,7 +6054,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>10641.28</v>
+        <v>11797.68</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -6409,7 +6409,7 @@
         <v>22671</v>
       </c>
       <c r="R43" t="n">
-        <v>344077.17</v>
+        <v>349093.17</v>
       </c>
       <c r="S43" t="n">
         <v>119213.37</v>
@@ -6418,7 +6418,7 @@
         <v>123149.37</v>
       </c>
       <c r="U43" t="n">
-        <v>174591.32</v>
+        <v>179607.32</v>
       </c>
       <c r="V43" t="n">
         <v>3936</v>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6671,7 +6671,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>825646.38</v>
+        <v>944859.7</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -6754,7 +6754,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6811,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3140108.86</v>
+        <v>3156507.76</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>7363410.03</v>
+        <v>7612695.77</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>101693</v>
+        <v>86656</v>
       </c>
       <c r="X54" t="n">
         <v>101693</v>
@@ -7973,10 +7973,10 @@
         <v>15037</v>
       </c>
       <c r="Z54" t="n">
-        <v>0</v>
+        <v>15037</v>
       </c>
       <c r="AA54" t="n">
-        <v>101693</v>
+        <v>86656</v>
       </c>
       <c r="AB54" t="n">
         <v>5</v>
@@ -8014,7 +8014,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8154,7 +8154,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8524,7 +8524,7 @@
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>20000</v>
+        <v>16354</v>
       </c>
       <c r="X58" t="n">
         <v>20000</v>
@@ -8533,10 +8533,10 @@
         <v>3646</v>
       </c>
       <c r="Z58" t="n">
-        <v>0</v>
+        <v>3646</v>
       </c>
       <c r="AA58" t="n">
-        <v>20000</v>
+        <v>16354</v>
       </c>
       <c r="AB58" t="n">
         <v>5</v>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>8643538.5</v>
+        <v>9154192.5</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
@@ -8664,7 +8664,7 @@
         <v>5679708.17</v>
       </c>
       <c r="W59" t="n">
-        <v>21191612.28</v>
+        <v>18518759</v>
       </c>
       <c r="X59" t="n">
         <v>22965724</v>
@@ -8673,10 +8673,10 @@
         <v>4186869</v>
       </c>
       <c r="Z59" t="n">
-        <v>1774111.72</v>
+        <v>4446965</v>
       </c>
       <c r="AA59" t="n">
-        <v>21191612.28</v>
+        <v>18518759</v>
       </c>
       <c r="AB59" t="n">
         <v>5</v>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9834,7 +9834,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10114,7 +10114,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
       </c>
       <c r="AJ71" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10674,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11094,7 +11094,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11514,7 +11514,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11794,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12214,7 +12214,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
         <v>350000</v>
       </c>
       <c r="O86" t="n">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="P86" t="n">
         <v>0</v>
@@ -12494,7 +12494,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12774,7 +12774,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -12864,7 +12864,7 @@
         <v>0</v>
       </c>
       <c r="W89" t="n">
-        <v>49592</v>
+        <v>25389</v>
       </c>
       <c r="X89" t="n">
         <v>49592</v>
@@ -12873,10 +12873,10 @@
         <v>24203</v>
       </c>
       <c r="Z89" t="n">
-        <v>0</v>
+        <v>24203</v>
       </c>
       <c r="AA89" t="n">
-        <v>49592</v>
+        <v>25389</v>
       </c>
       <c r="AB89" t="n">
         <v>5</v>
@@ -12914,7 +12914,7 @@
       </c>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13054,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13194,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13260,7 +13260,7 @@
         <v>366101.6</v>
       </c>
       <c r="O92" t="n">
-        <v>0</v>
+        <v>190000</v>
       </c>
       <c r="P92" t="n">
         <v>0</v>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13754,7 @@
       </c>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14034,7 +14034,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14174,7 +14174,7 @@
       </c>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14314,7 +14314,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14454,7 +14454,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14594,7 +14594,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15154,7 +15154,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15294,7 +15294,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15491,7 +15491,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>286730.01</v>
+        <v>317782.4</v>
       </c>
       <c r="M108" t="n">
         <v>0</v>
@@ -15524,7 +15524,7 @@
         <v>0</v>
       </c>
       <c r="W108" t="n">
-        <v>863000</v>
+        <v>690212.22</v>
       </c>
       <c r="X108" t="n">
         <v>863000</v>
@@ -15533,10 +15533,10 @@
         <v>246945</v>
       </c>
       <c r="Z108" t="n">
-        <v>0</v>
+        <v>172787.78</v>
       </c>
       <c r="AA108" t="n">
-        <v>863000</v>
+        <v>690212.22</v>
       </c>
       <c r="AB108" t="n">
         <v>5</v>
@@ -15574,7 +15574,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
         <v>1350</v>
       </c>
       <c r="W109" t="n">
-        <v>1074953</v>
+        <v>355872.78</v>
       </c>
       <c r="X109" t="n">
         <v>1314953</v>
@@ -15673,10 +15673,10 @@
         <v>719080.22</v>
       </c>
       <c r="Z109" t="n">
-        <v>240000</v>
+        <v>959080.22</v>
       </c>
       <c r="AA109" t="n">
-        <v>1074953</v>
+        <v>355872.78</v>
       </c>
       <c r="AB109" t="n">
         <v>5</v>
@@ -15714,7 +15714,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15854,7 +15854,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16134,7 +16134,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16274,7 +16274,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16504,7 +16504,7 @@
         <v>0</v>
       </c>
       <c r="W115" t="n">
-        <v>71950.39999999999</v>
+        <v>61773.4</v>
       </c>
       <c r="X115" t="n">
         <v>80000</v>
@@ -16513,10 +16513,10 @@
         <v>10177</v>
       </c>
       <c r="Z115" t="n">
-        <v>8049.6</v>
+        <v>18226.6</v>
       </c>
       <c r="AA115" t="n">
-        <v>71950.39999999999</v>
+        <v>61773.4</v>
       </c>
       <c r="AB115" t="n">
         <v>5</v>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16784,7 +16784,7 @@
         <v>0</v>
       </c>
       <c r="W117" t="n">
-        <v>450000</v>
+        <v>392752</v>
       </c>
       <c r="X117" t="n">
         <v>450000</v>
@@ -16793,10 +16793,10 @@
         <v>57248</v>
       </c>
       <c r="Z117" t="n">
-        <v>0</v>
+        <v>57248</v>
       </c>
       <c r="AA117" t="n">
-        <v>450000</v>
+        <v>392752</v>
       </c>
       <c r="AB117" t="n">
         <v>5</v>
@@ -16834,7 +16834,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17114,7 +17114,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17254,7 +17254,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17394,7 +17394,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17534,7 +17534,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17674,7 +17674,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17814,7 +17814,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -17904,7 +17904,7 @@
         <v>0</v>
       </c>
       <c r="W125" t="n">
-        <v>50000</v>
+        <v>345.28</v>
       </c>
       <c r="X125" t="n">
         <v>50000</v>
@@ -17913,10 +17913,10 @@
         <v>99125.72</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>49654.72</v>
       </c>
       <c r="AA125" t="n">
-        <v>50000</v>
+        <v>345.28</v>
       </c>
       <c r="AB125" t="n">
         <v>5</v>
@@ -17954,7 +17954,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18094,7 +18094,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18184,7 +18184,7 @@
         <v>0</v>
       </c>
       <c r="W127" t="n">
-        <v>47536.19</v>
+        <v>26594.19</v>
       </c>
       <c r="X127" t="n">
         <v>50000</v>
@@ -18193,10 +18193,10 @@
         <v>70413</v>
       </c>
       <c r="Z127" t="n">
-        <v>2463.81</v>
+        <v>23405.81</v>
       </c>
       <c r="AA127" t="n">
-        <v>47536.19</v>
+        <v>26594.19</v>
       </c>
       <c r="AB127" t="n">
         <v>5</v>
@@ -18234,7 +18234,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18324,7 +18324,7 @@
         <v>0</v>
       </c>
       <c r="W128" t="n">
-        <v>1253000</v>
+        <v>42000</v>
       </c>
       <c r="X128" t="n">
         <v>1261000</v>
@@ -18333,10 +18333,10 @@
         <v>1261000</v>
       </c>
       <c r="Z128" t="n">
-        <v>8000</v>
+        <v>1219000</v>
       </c>
       <c r="AA128" t="n">
-        <v>1253000</v>
+        <v>42000</v>
       </c>
       <c r="AB128" t="n">
         <v>5</v>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18514,7 +18514,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18604,7 @@
         <v>0</v>
       </c>
       <c r="W130" t="n">
-        <v>550500</v>
+        <v>0</v>
       </c>
       <c r="X130" t="n">
         <v>550500</v>
@@ -18613,10 +18613,10 @@
         <v>550500</v>
       </c>
       <c r="Z130" t="n">
-        <v>0</v>
+        <v>550500</v>
       </c>
       <c r="AA130" t="n">
-        <v>550500</v>
+        <v>0</v>
       </c>
       <c r="AB130" t="n">
         <v>5</v>
@@ -18654,7 +18654,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -18934,7 +18934,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19214,7 +19214,7 @@
       </c>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19494,7 +19494,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19634,7 +19634,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19774,7 +19774,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -19914,7 +19914,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20194,7 +20194,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20269,7 +20269,7 @@
         <v>0</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="S142" t="n">
         <v>0</v>
@@ -20278,7 +20278,7 @@
         <v>0</v>
       </c>
       <c r="U142" t="n">
-        <v>0</v>
+        <v>185000</v>
       </c>
       <c r="V142" t="n">
         <v>0</v>
@@ -20334,7 +20334,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20474,7 +20474,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20614,7 +20614,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20754,7 +20754,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -20894,7 +20894,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21034,7 +21034,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21124,7 +21124,7 @@
         <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>12421782</v>
+        <v>9813947</v>
       </c>
       <c r="X148" t="n">
         <v>12421782</v>
@@ -21133,10 +21133,10 @@
         <v>2607835</v>
       </c>
       <c r="Z148" t="n">
-        <v>0</v>
+        <v>2607835</v>
       </c>
       <c r="AA148" t="n">
-        <v>12421782</v>
+        <v>9813947</v>
       </c>
       <c r="AB148" t="n">
         <v>5</v>
@@ -21174,7 +21174,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21264,7 +21264,7 @@
         <v>0</v>
       </c>
       <c r="W149" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="X149" t="n">
         <v>56000</v>
@@ -21273,10 +21273,10 @@
         <v>56000</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>56000</v>
       </c>
       <c r="AA149" t="n">
-        <v>56000</v>
+        <v>0</v>
       </c>
       <c r="AB149" t="n">
         <v>5</v>
@@ -21314,7 +21314,7 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21454,7 +21454,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21594,7 +21594,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22014,7 +22014,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22384,7 +22384,7 @@
         <v>0</v>
       </c>
       <c r="W157" t="n">
-        <v>100000</v>
+        <v>75262</v>
       </c>
       <c r="X157" t="n">
         <v>100000</v>
@@ -22393,10 +22393,10 @@
         <v>24738</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>24738</v>
       </c>
       <c r="AA157" t="n">
-        <v>100000</v>
+        <v>75262</v>
       </c>
       <c r="AB157" t="n">
         <v>5</v>
@@ -22434,7 +22434,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22524,7 +22524,7 @@
         <v>11000</v>
       </c>
       <c r="W158" t="n">
-        <v>7704296</v>
+        <v>7639296</v>
       </c>
       <c r="X158" t="n">
         <v>8429440</v>
@@ -22533,10 +22533,10 @@
         <v>65000</v>
       </c>
       <c r="Z158" t="n">
-        <v>725144</v>
+        <v>790144</v>
       </c>
       <c r="AA158" t="n">
-        <v>7704296</v>
+        <v>7639296</v>
       </c>
       <c r="AB158" t="n">
         <v>5</v>
@@ -22574,7 +22574,7 @@
       </c>
       <c r="AJ158" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22714,7 +22714,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22804,7 +22804,7 @@
         <v>0</v>
       </c>
       <c r="W160" t="n">
-        <v>663648</v>
+        <v>385648</v>
       </c>
       <c r="X160" t="n">
         <v>867556</v>
@@ -22813,10 +22813,10 @@
         <v>278000</v>
       </c>
       <c r="Z160" t="n">
-        <v>203908</v>
+        <v>481908</v>
       </c>
       <c r="AA160" t="n">
-        <v>663648</v>
+        <v>385648</v>
       </c>
       <c r="AB160" t="n">
         <v>5</v>
@@ -22854,7 +22854,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -22994,7 +22994,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23134,7 +23134,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23274,7 +23274,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23554,7 +23554,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23694,7 +23694,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23834,7 +23834,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -23974,7 +23974,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24031,7 +24031,7 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>566909.84</v>
+        <v>647896.96</v>
       </c>
       <c r="M169" t="n">
         <v>0</v>
@@ -24064,7 +24064,7 @@
         <v>0</v>
       </c>
       <c r="W169" t="n">
-        <v>1111269</v>
+        <v>1083437</v>
       </c>
       <c r="X169" t="n">
         <v>547269</v>
@@ -24073,10 +24073,10 @@
         <v>27832</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>27832</v>
       </c>
       <c r="AA169" t="n">
-        <v>1111269</v>
+        <v>1083437</v>
       </c>
       <c r="AB169" t="n">
         <v>5</v>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24171,7 +24171,7 @@
         </is>
       </c>
       <c r="L170" t="n">
-        <v>1809344.33</v>
+        <v>1923344.33</v>
       </c>
       <c r="M170" t="n">
         <v>0</v>
@@ -24254,7 +24254,7 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24311,7 +24311,7 @@
         </is>
       </c>
       <c r="L171" t="n">
-        <v>147652.91</v>
+        <v>181507.55</v>
       </c>
       <c r="M171" t="n">
         <v>0</v>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24534,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24674,7 +24674,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24814,7 +24814,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -24954,7 +24954,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25044,7 +25044,7 @@
         <v>0</v>
       </c>
       <c r="W176" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="X176" t="n">
         <v>10000</v>
@@ -25053,10 +25053,10 @@
         <v>10000</v>
       </c>
       <c r="Z176" t="n">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="AA176" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="AB176" t="n">
         <v>5</v>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="AJ176" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25234,7 +25234,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25374,7 +25374,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25514,7 +25514,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25654,7 +25654,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -25860,7 +25860,7 @@
         <v>100000</v>
       </c>
       <c r="O182" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="P182" t="n">
         <v>0</v>
@@ -25934,7 +25934,7 @@
       </c>
       <c r="AJ182" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26074,7 +26074,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26214,7 +26214,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26354,7 +26354,7 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26420,7 +26420,7 @@
         <v>578000</v>
       </c>
       <c r="O186" t="n">
-        <v>350000</v>
+        <v>578000</v>
       </c>
       <c r="P186" t="n">
         <v>0</v>
@@ -26494,7 +26494,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26634,7 +26634,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="AJ188" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -26831,7 +26831,7 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>150000</v>
+        <v>261000</v>
       </c>
       <c r="M189" t="n">
         <v>0</v>
@@ -26840,7 +26840,7 @@
         <v>261000</v>
       </c>
       <c r="O189" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="P189" t="n">
         <v>0</v>
@@ -26914,7 +26914,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27054,7 +27054,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27334,7 +27334,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27474,7 +27474,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27614,7 +27614,7 @@
       </c>
       <c r="AJ194" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27754,7 +27754,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27894,7 +27894,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -27951,7 +27951,7 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>869016.0600000001</v>
+        <v>898725.67</v>
       </c>
       <c r="M197" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
       </c>
       <c r="AJ197" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28091,7 +28091,7 @@
         </is>
       </c>
       <c r="L198" t="n">
-        <v>1709187.91</v>
+        <v>1736975.36</v>
       </c>
       <c r="M198" t="n">
         <v>0</v>
@@ -28124,7 +28124,7 @@
         <v>104347.76</v>
       </c>
       <c r="W198" t="n">
-        <v>3393577.03</v>
+        <v>3328090.03</v>
       </c>
       <c r="X198" t="n">
         <v>4806049</v>
@@ -28133,10 +28133,10 @@
         <v>65487</v>
       </c>
       <c r="Z198" t="n">
-        <v>1412471.97</v>
+        <v>1477958.97</v>
       </c>
       <c r="AA198" t="n">
-        <v>3393577.03</v>
+        <v>3328090.03</v>
       </c>
       <c r="AB198" t="n">
         <v>5</v>
@@ -28174,7 +28174,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28314,7 +28314,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="AJ200" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28544,7 +28544,7 @@
         <v>0</v>
       </c>
       <c r="W201" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="X201" t="n">
         <v>110000</v>
@@ -28553,10 +28553,10 @@
         <v>330000</v>
       </c>
       <c r="Z201" t="n">
-        <v>109000</v>
+        <v>110000</v>
       </c>
       <c r="AA201" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB201" t="n">
         <v>5</v>
@@ -28594,7 +28594,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28734,7 +28734,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28874,7 +28874,7 @@
       </c>
       <c r="AJ203" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -28949,7 +28949,7 @@
         <v>0</v>
       </c>
       <c r="R204" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="S204" t="n">
         <v>0</v>
@@ -28958,7 +28958,7 @@
         <v>0</v>
       </c>
       <c r="U204" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="V204" t="n">
         <v>0</v>
@@ -29014,7 +29014,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29154,7 +29154,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29294,7 +29294,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29434,7 +29434,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29524,7 +29524,7 @@
         <v>0</v>
       </c>
       <c r="W208" t="n">
-        <v>150000</v>
+        <v>80612</v>
       </c>
       <c r="X208" t="n">
         <v>150000</v>
@@ -29533,10 +29533,10 @@
         <v>69388</v>
       </c>
       <c r="Z208" t="n">
-        <v>0</v>
+        <v>69388</v>
       </c>
       <c r="AA208" t="n">
-        <v>150000</v>
+        <v>80612</v>
       </c>
       <c r="AB208" t="n">
         <v>5</v>
@@ -29574,7 +29574,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29631,7 +29631,7 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>318485.12</v>
+        <v>356543.33</v>
       </c>
       <c r="M209" t="n">
         <v>0</v>
@@ -29664,7 +29664,7 @@
         <v>1894229.63</v>
       </c>
       <c r="W209" t="n">
-        <v>5633981</v>
+        <v>4801538</v>
       </c>
       <c r="X209" t="n">
         <v>10925362</v>
@@ -29673,10 +29673,10 @@
         <v>5886824</v>
       </c>
       <c r="Z209" t="n">
-        <v>5291381</v>
+        <v>6123824</v>
       </c>
       <c r="AA209" t="n">
-        <v>5633981</v>
+        <v>4801538</v>
       </c>
       <c r="AB209" t="n">
         <v>5</v>
@@ -29714,7 +29714,7 @@
       </c>
       <c r="AJ209" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29854,7 +29854,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -29994,7 +29994,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30060,7 +30060,7 @@
         <v>0</v>
       </c>
       <c r="O212" t="n">
-        <v>24800</v>
+        <v>28300</v>
       </c>
       <c r="P212" t="n">
         <v>11400</v>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="AJ212" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30224,7 +30224,7 @@
         <v>0</v>
       </c>
       <c r="W213" t="n">
-        <v>298719</v>
+        <v>111422</v>
       </c>
       <c r="X213" t="n">
         <v>220966</v>
@@ -30233,10 +30233,10 @@
         <v>187297</v>
       </c>
       <c r="Z213" t="n">
-        <v>0</v>
+        <v>187297</v>
       </c>
       <c r="AA213" t="n">
-        <v>298719</v>
+        <v>111422</v>
       </c>
       <c r="AB213" t="n">
         <v>5</v>
@@ -30274,7 +30274,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30414,7 +30414,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30554,7 +30554,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30694,7 +30694,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30834,7 +30834,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -30900,7 +30900,7 @@
         <v>200000</v>
       </c>
       <c r="O218" t="n">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="P218" t="n">
         <v>0</v>
@@ -30974,7 +30974,7 @@
       </c>
       <c r="AJ218" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31064,7 +31064,7 @@
         <v>0</v>
       </c>
       <c r="W219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="X219" t="n">
         <v>589773</v>
@@ -31073,10 +31073,10 @@
         <v>589773</v>
       </c>
       <c r="Z219" t="n">
-        <v>0</v>
+        <v>589773</v>
       </c>
       <c r="AA219" t="n">
-        <v>589773</v>
+        <v>0</v>
       </c>
       <c r="AB219" t="n">
         <v>5</v>
@@ -31114,7 +31114,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31394,7 +31394,7 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31534,7 +31534,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31674,7 +31674,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31731,7 +31731,7 @@
         </is>
       </c>
       <c r="L224" t="n">
-        <v>143354924.45</v>
+        <v>145326699.52</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
@@ -31743,16 +31743,16 @@
         <v>143214278.92</v>
       </c>
       <c r="P224" t="n">
-        <v>50430560.11</v>
+        <v>50520982.11</v>
       </c>
       <c r="Q224" t="n">
         <v>5735947</v>
       </c>
       <c r="R224" t="n">
-        <v>216144682.06</v>
+        <v>216235104.06</v>
       </c>
       <c r="S224" t="n">
-        <v>163960267.15</v>
+        <v>163869845.15</v>
       </c>
       <c r="T224" t="n">
         <v>170144602.81</v>
@@ -31761,10 +31761,10 @@
         <v>165714121.95</v>
       </c>
       <c r="V224" t="n">
-        <v>6184335.66</v>
+        <v>6274757.66</v>
       </c>
       <c r="W224" t="n">
-        <v>166364878.87</v>
+        <v>165715582</v>
       </c>
       <c r="X224" t="n">
         <v>171813039</v>
@@ -31773,10 +31773,10 @@
         <v>5735947</v>
       </c>
       <c r="Z224" t="n">
-        <v>5448160.13</v>
+        <v>6097457</v>
       </c>
       <c r="AA224" t="n">
-        <v>166364878.87</v>
+        <v>165715582</v>
       </c>
       <c r="AB224" t="n">
         <v>5</v>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -31954,7 +31954,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32094,7 +32094,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32151,7 +32151,7 @@
         </is>
       </c>
       <c r="L227" t="n">
-        <v>81734533.70999999</v>
+        <v>83680665.70999999</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -32234,7 +32234,7 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32300,7 +32300,7 @@
         <v>0</v>
       </c>
       <c r="O228" t="n">
-        <v>58633632.9</v>
+        <v>61063632.9</v>
       </c>
       <c r="P228" t="n">
         <v>51388595.59</v>
@@ -32324,7 +32324,7 @@
         <v>20893793.67</v>
       </c>
       <c r="W228" t="n">
-        <v>82235403</v>
+        <v>79443026</v>
       </c>
       <c r="X228" t="n">
         <v>83642123</v>
@@ -32333,10 +32333,10 @@
         <v>2792377</v>
       </c>
       <c r="Z228" t="n">
-        <v>1406720</v>
+        <v>4199097</v>
       </c>
       <c r="AA228" t="n">
-        <v>82235403</v>
+        <v>79443026</v>
       </c>
       <c r="AB228" t="n">
         <v>5</v>
@@ -32374,7 +32374,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32514,7 +32514,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32654,7 +32654,7 @@
       </c>
       <c r="AJ230" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32794,7 +32794,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -32934,7 +32934,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -33074,7 +33074,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -33214,7 +33214,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
@@ -33280,7 +33280,7 @@
         <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>36646414.73</v>
+        <v>37249300.96</v>
       </c>
       <c r="P235" t="n">
         <v>8356750.31</v>
@@ -33292,10 +33292,10 @@
         <v>51905693.91</v>
       </c>
       <c r="S235" t="n">
-        <v>41221083.35</v>
+        <v>41383303.35</v>
       </c>
       <c r="T235" t="n">
-        <v>42833847.51</v>
+        <v>42996067.51</v>
       </c>
       <c r="U235" t="n">
         <v>43548943.6</v>
@@ -33354,7 +33354,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>29/09/2026 12:52:47</t>
+          <t>30/09/2026 12:58:00</t>
         </is>
       </c>
     </row>
